--- a/IEF_Home/UploadedFiles/3_MC_Buildings_Odense_Lanau_2020.xlsx
+++ b/IEF_Home/UploadedFiles/3_MC_Buildings_Odense_Lanau_2020.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20416"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{856650B8-4BD6-41C1-9AC8-1B088D73DB9E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB97907-D5C5-4F61-859A-DA39CC61B284}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16800" yWindow="440" windowWidth="21600" windowHeight="23480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="168">
   <si>
     <t>Format_Version</t>
   </si>
@@ -520,9 +520,6 @@
   </si>
   <si>
     <t>aggregates (other than in concrete)</t>
-  </si>
-  <si>
-    <t>apartment buildingx</t>
   </si>
 </sst>
 </file>
@@ -982,6 +979,21 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1008,21 +1020,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1382,20 +1379,20 @@
       <c r="H1" s="8"/>
     </row>
     <row r="2" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="79" t="s">
+      <c r="B2" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="81"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="86"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="79" t="s">
+      <c r="F2" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="81"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="86"/>
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
@@ -1414,7 +1411,7 @@
       <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="82" t="s">
+      <c r="B4" s="87" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -1440,7 +1437,7 @@
       <c r="A5" s="11">
         <v>2</v>
       </c>
-      <c r="B5" s="83"/>
+      <c r="B5" s="88"/>
       <c r="C5" s="20" t="s">
         <v>28</v>
       </c>
@@ -1492,7 +1489,7 @@
       <c r="A7" s="11">
         <v>4</v>
       </c>
-      <c r="B7" s="84" t="s">
+      <c r="B7" s="89" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -1524,7 +1521,7 @@
       <c r="A8" s="11">
         <v>5</v>
       </c>
-      <c r="B8" s="84"/>
+      <c r="B8" s="89"/>
       <c r="C8" s="20" t="s">
         <v>35</v>
       </c>
@@ -1552,7 +1549,7 @@
       <c r="A9" s="11">
         <v>6</v>
       </c>
-      <c r="B9" s="84"/>
+      <c r="B9" s="89"/>
       <c r="C9" s="20" t="s">
         <v>36</v>
       </c>
@@ -1580,7 +1577,7 @@
       <c r="A10" s="11">
         <v>7</v>
       </c>
-      <c r="B10" s="84"/>
+      <c r="B10" s="89"/>
       <c r="C10" s="20" t="s">
         <v>37</v>
       </c>
@@ -1614,7 +1611,7 @@
       <c r="A11" s="11">
         <v>8</v>
       </c>
-      <c r="B11" s="85" t="s">
+      <c r="B11" s="90" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="35" t="s">
@@ -1650,7 +1647,7 @@
       <c r="A12" s="11">
         <v>9</v>
       </c>
-      <c r="B12" s="86"/>
+      <c r="B12" s="91"/>
       <c r="C12" s="38" t="s">
         <v>40</v>
       </c>
@@ -1684,7 +1681,7 @@
       <c r="A13" s="11">
         <v>10</v>
       </c>
-      <c r="B13" s="86"/>
+      <c r="B13" s="91"/>
       <c r="C13" s="38" t="s">
         <v>41</v>
       </c>
@@ -1714,7 +1711,7 @@
       <c r="A14" s="11">
         <v>11</v>
       </c>
-      <c r="B14" s="86"/>
+      <c r="B14" s="91"/>
       <c r="C14" s="38" t="s">
         <v>42</v>
       </c>
@@ -1740,7 +1737,7 @@
       <c r="A15" s="11">
         <v>12</v>
       </c>
-      <c r="B15" s="86"/>
+      <c r="B15" s="91"/>
       <c r="C15" s="38" t="s">
         <v>43</v>
       </c>
@@ -1766,7 +1763,7 @@
       <c r="A16" s="11">
         <v>13</v>
       </c>
-      <c r="B16" s="86"/>
+      <c r="B16" s="91"/>
       <c r="C16" s="38" t="s">
         <v>44</v>
       </c>
@@ -1788,7 +1785,7 @@
       <c r="A17" s="11">
         <v>14</v>
       </c>
-      <c r="B17" s="86"/>
+      <c r="B17" s="91"/>
       <c r="C17" s="38" t="s">
         <v>45</v>
       </c>
@@ -1810,7 +1807,7 @@
       <c r="A18" s="11">
         <v>15</v>
       </c>
-      <c r="B18" s="86"/>
+      <c r="B18" s="91"/>
       <c r="C18" s="38" t="s">
         <v>46</v>
       </c>
@@ -1832,7 +1829,7 @@
       <c r="A19" s="11">
         <v>16</v>
       </c>
-      <c r="B19" s="86"/>
+      <c r="B19" s="91"/>
       <c r="C19" s="38" t="s">
         <v>47</v>
       </c>
@@ -1854,7 +1851,7 @@
       <c r="A20" s="11">
         <v>17</v>
       </c>
-      <c r="B20" s="86"/>
+      <c r="B20" s="91"/>
       <c r="C20" s="38" t="s">
         <v>48</v>
       </c>
@@ -1876,7 +1873,7 @@
       <c r="A21" s="11">
         <v>18</v>
       </c>
-      <c r="B21" s="87" t="s">
+      <c r="B21" s="92" t="s">
         <v>49</v>
       </c>
       <c r="C21" s="38" t="s">
@@ -1900,7 +1897,7 @@
       <c r="A22" s="11">
         <v>19</v>
       </c>
-      <c r="B22" s="87"/>
+      <c r="B22" s="92"/>
       <c r="C22" s="38" t="s">
         <v>51</v>
       </c>
@@ -1918,7 +1915,7 @@
       <c r="A23" s="11">
         <v>20</v>
       </c>
-      <c r="B23" s="87"/>
+      <c r="B23" s="92"/>
       <c r="C23" s="35" t="s">
         <v>52</v>
       </c>
@@ -1936,7 +1933,7 @@
       <c r="A24" s="11">
         <v>21</v>
       </c>
-      <c r="B24" s="87"/>
+      <c r="B24" s="92"/>
       <c r="C24" s="35" t="s">
         <v>53</v>
       </c>
@@ -1954,7 +1951,7 @@
       <c r="A25" s="11">
         <v>22</v>
       </c>
-      <c r="B25" s="87"/>
+      <c r="B25" s="92"/>
       <c r="C25" s="38" t="s">
         <v>54</v>
       </c>
@@ -1972,7 +1969,7 @@
       <c r="A26" s="11">
         <v>23</v>
       </c>
-      <c r="B26" s="88" t="s">
+      <c r="B26" s="79" t="s">
         <v>55</v>
       </c>
       <c r="C26" s="55" t="s">
@@ -1992,7 +1989,7 @@
       <c r="A27" s="11">
         <v>24</v>
       </c>
-      <c r="B27" s="88"/>
+      <c r="B27" s="79"/>
       <c r="C27" s="55" t="s">
         <v>57</v>
       </c>
@@ -2012,7 +2009,7 @@
       <c r="A28" s="11">
         <v>25</v>
       </c>
-      <c r="B28" s="88"/>
+      <c r="B28" s="79"/>
       <c r="C28" s="55" t="s">
         <v>58</v>
       </c>
@@ -2031,7 +2028,7 @@
       <c r="A29" s="11">
         <v>26</v>
       </c>
-      <c r="B29" s="88"/>
+      <c r="B29" s="79"/>
       <c r="C29" s="55" t="s">
         <v>59</v>
       </c>
@@ -2064,7 +2061,7 @@
       <c r="A30" s="11">
         <v>27</v>
       </c>
-      <c r="B30" s="88"/>
+      <c r="B30" s="79"/>
       <c r="C30" s="55" t="s">
         <v>60</v>
       </c>
@@ -2097,7 +2094,7 @@
       <c r="A31" s="11">
         <v>28</v>
       </c>
-      <c r="B31" s="88"/>
+      <c r="B31" s="79"/>
       <c r="C31" s="55" t="s">
         <v>61</v>
       </c>
@@ -2130,7 +2127,7 @@
       <c r="A32" s="11">
         <v>29</v>
       </c>
-      <c r="B32" s="88"/>
+      <c r="B32" s="79"/>
       <c r="C32" s="55" t="s">
         <v>62</v>
       </c>
@@ -2163,7 +2160,7 @@
       <c r="A33" s="11">
         <v>30</v>
       </c>
-      <c r="B33" s="88"/>
+      <c r="B33" s="79"/>
       <c r="C33" s="55" t="s">
         <v>63</v>
       </c>
@@ -2197,7 +2194,7 @@
       <c r="A34" s="11">
         <v>31</v>
       </c>
-      <c r="B34" s="88"/>
+      <c r="B34" s="79"/>
       <c r="C34" s="55" t="s">
         <v>64</v>
       </c>
@@ -2231,7 +2228,7 @@
       <c r="A35" s="11">
         <v>32</v>
       </c>
-      <c r="B35" s="88"/>
+      <c r="B35" s="79"/>
       <c r="C35" s="55" t="s">
         <v>65</v>
       </c>
@@ -2265,7 +2262,7 @@
       <c r="A36" s="11">
         <v>33</v>
       </c>
-      <c r="B36" s="88"/>
+      <c r="B36" s="79"/>
       <c r="C36" s="55" t="s">
         <v>66</v>
       </c>
@@ -2299,7 +2296,7 @@
       <c r="A37" s="11">
         <v>34</v>
       </c>
-      <c r="B37" s="88"/>
+      <c r="B37" s="79"/>
       <c r="C37" s="55" t="s">
         <v>67</v>
       </c>
@@ -2326,7 +2323,7 @@
       <c r="A38" s="11">
         <v>35</v>
       </c>
-      <c r="B38" s="88"/>
+      <c r="B38" s="79"/>
       <c r="C38" s="55" t="s">
         <v>68</v>
       </c>
@@ -2353,7 +2350,7 @@
       <c r="A39" s="11">
         <v>36</v>
       </c>
-      <c r="B39" s="88"/>
+      <c r="B39" s="79"/>
       <c r="C39" s="55" t="s">
         <v>69</v>
       </c>
@@ -2380,7 +2377,7 @@
       <c r="A40" s="11">
         <v>37</v>
       </c>
-      <c r="B40" s="88"/>
+      <c r="B40" s="79"/>
       <c r="C40" s="55" t="s">
         <v>70</v>
       </c>
@@ -2407,7 +2404,7 @@
       <c r="A41" s="11">
         <v>38</v>
       </c>
-      <c r="B41" s="88"/>
+      <c r="B41" s="79"/>
       <c r="C41" s="55" t="s">
         <v>71</v>
       </c>
@@ -2434,7 +2431,7 @@
       <c r="A42" s="11">
         <v>39</v>
       </c>
-      <c r="B42" s="88"/>
+      <c r="B42" s="79"/>
       <c r="C42" s="55" t="s">
         <v>72</v>
       </c>
@@ -2461,7 +2458,7 @@
       <c r="A43" s="11">
         <v>40</v>
       </c>
-      <c r="B43" s="88"/>
+      <c r="B43" s="79"/>
       <c r="C43" s="55" t="s">
         <v>73</v>
       </c>
@@ -2488,7 +2485,7 @@
       <c r="A44" s="11">
         <v>41</v>
       </c>
-      <c r="B44" s="88"/>
+      <c r="B44" s="79"/>
       <c r="C44" s="55" t="s">
         <v>74</v>
       </c>
@@ -2515,7 +2512,7 @@
       <c r="A45" s="11">
         <v>42</v>
       </c>
-      <c r="B45" s="88"/>
+      <c r="B45" s="79"/>
       <c r="C45" s="55" t="s">
         <v>75</v>
       </c>
@@ -2542,7 +2539,7 @@
       <c r="A46" s="11">
         <v>43</v>
       </c>
-      <c r="B46" s="88"/>
+      <c r="B46" s="79"/>
       <c r="C46" s="55" t="s">
         <v>76</v>
       </c>
@@ -2569,7 +2566,7 @@
       <c r="A47" s="11">
         <v>44</v>
       </c>
-      <c r="B47" s="88"/>
+      <c r="B47" s="79"/>
       <c r="C47" s="55" t="s">
         <v>77</v>
       </c>
@@ -2596,7 +2593,7 @@
       <c r="A48" s="11">
         <v>45</v>
       </c>
-      <c r="B48" s="88"/>
+      <c r="B48" s="79"/>
       <c r="C48" s="55" t="s">
         <v>78</v>
       </c>
@@ -2623,7 +2620,7 @@
       <c r="A49" s="11">
         <v>46</v>
       </c>
-      <c r="B49" s="88"/>
+      <c r="B49" s="79"/>
       <c r="C49" s="55" t="s">
         <v>79</v>
       </c>
@@ -2650,7 +2647,7 @@
       <c r="A50" s="11">
         <v>47</v>
       </c>
-      <c r="B50" s="88"/>
+      <c r="B50" s="79"/>
       <c r="C50" s="35" t="s">
         <v>80</v>
       </c>
@@ -2677,7 +2674,7 @@
       <c r="A51" s="11">
         <v>48</v>
       </c>
-      <c r="B51" s="88"/>
+      <c r="B51" s="79"/>
       <c r="C51" s="35" t="s">
         <v>81</v>
       </c>
@@ -2704,7 +2701,7 @@
       <c r="A52" s="11">
         <v>49</v>
       </c>
-      <c r="B52" s="88"/>
+      <c r="B52" s="79"/>
       <c r="C52" s="35" t="s">
         <v>82</v>
       </c>
@@ -2731,7 +2728,7 @@
       <c r="A53" s="11">
         <v>50</v>
       </c>
-      <c r="B53" s="89" t="s">
+      <c r="B53" s="80" t="s">
         <v>83</v>
       </c>
       <c r="C53" s="20" t="s">
@@ -2760,7 +2757,7 @@
       <c r="A54" s="11">
         <v>51</v>
       </c>
-      <c r="B54" s="89"/>
+      <c r="B54" s="80"/>
       <c r="C54" s="20" t="s">
         <v>85</v>
       </c>
@@ -2787,7 +2784,7 @@
       <c r="A55" s="11">
         <v>52</v>
       </c>
-      <c r="B55" s="89"/>
+      <c r="B55" s="80"/>
       <c r="C55" s="58" t="s">
         <v>86</v>
       </c>
@@ -2816,7 +2813,7 @@
       <c r="A56" s="11">
         <v>53</v>
       </c>
-      <c r="B56" s="89"/>
+      <c r="B56" s="80"/>
       <c r="C56" s="58" t="s">
         <v>87</v>
       </c>
@@ -2843,7 +2840,7 @@
       <c r="A57" s="11">
         <v>54</v>
       </c>
-      <c r="B57" s="89"/>
+      <c r="B57" s="80"/>
       <c r="C57" s="38" t="s">
         <v>88</v>
       </c>
@@ -2870,7 +2867,7 @@
       <c r="A58" s="11">
         <v>55</v>
       </c>
-      <c r="B58" s="89"/>
+      <c r="B58" s="80"/>
       <c r="C58" s="58" t="s">
         <v>89</v>
       </c>
@@ -2897,7 +2894,7 @@
       <c r="A59" s="11">
         <v>56</v>
       </c>
-      <c r="B59" s="89"/>
+      <c r="B59" s="80"/>
       <c r="C59" s="58" t="s">
         <v>90</v>
       </c>
@@ -2924,7 +2921,7 @@
       <c r="A60" s="11">
         <v>57</v>
       </c>
-      <c r="B60" s="89"/>
+      <c r="B60" s="80"/>
       <c r="C60" s="20" t="s">
         <v>91</v>
       </c>
@@ -2951,7 +2948,7 @@
       <c r="A61" s="11">
         <v>58</v>
       </c>
-      <c r="B61" s="90" t="s">
+      <c r="B61" s="81" t="s">
         <v>92</v>
       </c>
       <c r="C61" s="58" t="s">
@@ -2980,7 +2977,7 @@
       <c r="A62" s="11">
         <v>59</v>
       </c>
-      <c r="B62" s="90"/>
+      <c r="B62" s="81"/>
       <c r="C62" s="58" t="s">
         <v>94</v>
       </c>
@@ -3007,7 +3004,7 @@
       <c r="A63" s="11">
         <v>60</v>
       </c>
-      <c r="B63" s="90"/>
+      <c r="B63" s="81"/>
       <c r="C63" s="58" t="s">
         <v>95</v>
       </c>
@@ -3034,7 +3031,7 @@
       <c r="A64" s="11">
         <v>61</v>
       </c>
-      <c r="B64" s="90"/>
+      <c r="B64" s="81"/>
       <c r="C64" s="58" t="s">
         <v>96</v>
       </c>
@@ -3061,7 +3058,7 @@
       <c r="A65" s="11">
         <v>62</v>
       </c>
-      <c r="B65" s="90"/>
+      <c r="B65" s="81"/>
       <c r="C65" s="20" t="s">
         <v>97</v>
       </c>
@@ -3086,7 +3083,7 @@
       <c r="A66" s="11">
         <v>63</v>
       </c>
-      <c r="B66" s="90"/>
+      <c r="B66" s="81"/>
       <c r="C66" s="20" t="s">
         <v>98</v>
       </c>
@@ -3099,7 +3096,7 @@
       <c r="A67" s="11">
         <v>64</v>
       </c>
-      <c r="B67" s="90"/>
+      <c r="B67" s="81"/>
       <c r="C67" s="58" t="s">
         <v>99</v>
       </c>
@@ -3112,7 +3109,7 @@
       <c r="A68" s="11">
         <v>65</v>
       </c>
-      <c r="B68" s="91" t="s">
+      <c r="B68" s="82" t="s">
         <v>100</v>
       </c>
       <c r="C68" s="60" t="s">
@@ -3127,7 +3124,7 @@
       <c r="A69" s="11">
         <v>66</v>
       </c>
-      <c r="B69" s="91"/>
+      <c r="B69" s="82"/>
       <c r="C69" s="60" t="s">
         <v>102</v>
       </c>
@@ -3140,7 +3137,7 @@
       <c r="A70" s="11">
         <v>67</v>
       </c>
-      <c r="B70" s="91"/>
+      <c r="B70" s="82"/>
       <c r="C70" s="60" t="s">
         <v>103</v>
       </c>
@@ -3153,7 +3150,7 @@
       <c r="A71" s="11">
         <v>68</v>
       </c>
-      <c r="B71" s="91"/>
+      <c r="B71" s="82"/>
       <c r="C71" s="60" t="s">
         <v>104</v>
       </c>
@@ -3166,7 +3163,7 @@
       <c r="A72" s="11">
         <v>69</v>
       </c>
-      <c r="B72" s="92"/>
+      <c r="B72" s="83"/>
       <c r="C72" s="61" t="s">
         <v>105</v>
       </c>
@@ -3177,16 +3174,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B7:B10"/>
+    <mergeCell ref="B11:B20"/>
+    <mergeCell ref="B21:B25"/>
     <mergeCell ref="B26:B52"/>
     <mergeCell ref="B53:B60"/>
     <mergeCell ref="B61:B67"/>
     <mergeCell ref="B68:B72"/>
     <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="B7:B10"/>
-    <mergeCell ref="B11:B20"/>
-    <mergeCell ref="B21:B25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7163,7 +7160,7 @@
         <v>120</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>168</v>
+        <v>124</v>
       </c>
       <c r="C91" s="23" t="s">
         <v>164</v>

--- a/IEF_Home/UploadedFiles/3_MC_Buildings_Odense_Lanau_2020.xlsx
+++ b/IEF_Home/UploadedFiles/3_MC_Buildings_Odense_Lanau_2020.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20416"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB97907-D5C5-4F61-859A-DA39CC61B284}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E27CD29-97BC-4ACA-8203-B6A643B72DCB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16800" yWindow="440" windowWidth="21600" windowHeight="23480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16800" yWindow="438" windowWidth="21600" windowHeight="23478" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -384,9 +384,6 @@
     <t>Odense, Denmark</t>
   </si>
   <si>
-    <t>single family house</t>
-  </si>
-  <si>
     <t>terraced house</t>
   </si>
   <si>
@@ -520,6 +517,9 @@
   </si>
   <si>
     <t>aggregates (other than in concrete)</t>
+  </si>
+  <si>
+    <t>single-family house</t>
   </si>
 </sst>
 </file>
@@ -979,21 +979,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1020,6 +1005,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1360,42 +1360,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC72"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1015625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="7.08984375" customWidth="1"/>
-    <col min="2" max="2" width="15.81640625" customWidth="1"/>
-    <col min="3" max="3" width="23.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="46.81640625" customWidth="1"/>
-    <col min="5" max="5" width="11.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.1015625" customWidth="1"/>
+    <col min="2" max="2" width="15.7890625" customWidth="1"/>
+    <col min="3" max="3" width="23.1015625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="46.7890625" customWidth="1"/>
+    <col min="5" max="5" width="11.62890625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.26171875" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="26" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" customWidth="1"/>
-    <col min="11" max="11" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24.7890625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7890625" customWidth="1"/>
+    <col min="11" max="11" width="15.47265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="E1" s="1"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:12" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="B2" s="84" t="s">
+    <row r="2" spans="1:12" ht="15.6" x14ac:dyDescent="0.6">
+      <c r="B2" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="85"/>
-      <c r="D2" s="86"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="81"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="84" t="s">
+      <c r="F2" s="79" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="85"/>
-      <c r="H2" s="85"/>
-      <c r="I2" s="85"/>
-      <c r="J2" s="85"/>
-      <c r="K2" s="86"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
+      <c r="J2" s="80"/>
+      <c r="K2" s="81"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="11"/>
       <c r="B3" s="12"/>
       <c r="C3" s="13" t="s">
@@ -1407,11 +1407,11 @@
       <c r="E3" s="1"/>
       <c r="L3" s="1"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="82" t="s">
         <v>24</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -1433,11 +1433,11 @@
       <c r="K4" s="19"/>
       <c r="L4" s="1"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="11">
         <v>2</v>
       </c>
-      <c r="B5" s="88"/>
+      <c r="B5" s="83"/>
       <c r="C5" s="20" t="s">
         <v>28</v>
       </c>
@@ -1455,7 +1455,7 @@
       <c r="K5" s="24"/>
       <c r="L5" s="1"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="11">
         <v>3</v>
       </c>
@@ -1485,11 +1485,11 @@
       <c r="K6" s="24"/>
       <c r="L6" s="1"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="11">
         <v>4</v>
       </c>
-      <c r="B7" s="89" t="s">
+      <c r="B7" s="84" t="s">
         <v>33</v>
       </c>
       <c r="C7" s="20" t="s">
@@ -1517,11 +1517,11 @@
       <c r="K7" s="24"/>
       <c r="L7" s="1"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="11">
         <v>5</v>
       </c>
-      <c r="B8" s="89"/>
+      <c r="B8" s="84"/>
       <c r="C8" s="20" t="s">
         <v>35</v>
       </c>
@@ -1545,11 +1545,11 @@
       <c r="K8" s="24"/>
       <c r="L8" s="1"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="11">
         <v>6</v>
       </c>
-      <c r="B9" s="89"/>
+      <c r="B9" s="84"/>
       <c r="C9" s="20" t="s">
         <v>36</v>
       </c>
@@ -1573,11 +1573,11 @@
       <c r="K9" s="24"/>
       <c r="L9" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="11">
         <v>7</v>
       </c>
-      <c r="B10" s="89"/>
+      <c r="B10" s="84"/>
       <c r="C10" s="20" t="s">
         <v>37</v>
       </c>
@@ -1607,11 +1607,11 @@
       </c>
       <c r="L10" s="1"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="11">
         <v>8</v>
       </c>
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="85" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="35" t="s">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="11">
         <v>9</v>
       </c>
-      <c r="B12" s="91"/>
+      <c r="B12" s="86"/>
       <c r="C12" s="38" t="s">
         <v>40</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="39" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G12" s="40">
         <v>1</v>
@@ -1677,22 +1677,22 @@
       </c>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="11">
         <v>10</v>
       </c>
-      <c r="B13" s="91"/>
+      <c r="B13" s="86"/>
       <c r="C13" s="38" t="s">
         <v>41</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F13" s="39" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G13" s="40">
         <v>1</v>
@@ -1707,16 +1707,16 @@
       </c>
       <c r="L13" s="1"/>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="11">
         <v>11</v>
       </c>
-      <c r="B14" s="91"/>
+      <c r="B14" s="86"/>
       <c r="C14" s="38" t="s">
         <v>42</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>14</v>
@@ -1733,11 +1733,11 @@
       <c r="K14" s="47"/>
       <c r="L14" s="1"/>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="11">
         <v>12</v>
       </c>
-      <c r="B15" s="91"/>
+      <c r="B15" s="86"/>
       <c r="C15" s="38" t="s">
         <v>43</v>
       </c>
@@ -1759,16 +1759,16 @@
       <c r="K15" s="47"/>
       <c r="L15" s="1"/>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="11">
         <v>13</v>
       </c>
-      <c r="B16" s="91"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="38" t="s">
         <v>44</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>14</v>
@@ -1781,11 +1781,11 @@
       <c r="K16" s="50"/>
       <c r="L16" s="1"/>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="11">
         <v>14</v>
       </c>
-      <c r="B17" s="91"/>
+      <c r="B17" s="86"/>
       <c r="C17" s="38" t="s">
         <v>45</v>
       </c>
@@ -1803,16 +1803,16 @@
       <c r="K17" s="51"/>
       <c r="L17" s="1"/>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="11">
         <v>15</v>
       </c>
-      <c r="B18" s="91"/>
+      <c r="B18" s="86"/>
       <c r="C18" s="38" t="s">
         <v>46</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>14</v>
@@ -1825,16 +1825,16 @@
       <c r="K18" s="51"/>
       <c r="L18" s="1"/>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="11">
         <v>16</v>
       </c>
-      <c r="B19" s="91"/>
+      <c r="B19" s="86"/>
       <c r="C19" s="38" t="s">
         <v>47</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>14</v>
@@ -1847,16 +1847,16 @@
       <c r="K19" s="51"/>
       <c r="L19" s="1"/>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="11">
         <v>17</v>
       </c>
-      <c r="B20" s="91"/>
+      <c r="B20" s="86"/>
       <c r="C20" s="38" t="s">
         <v>48</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>14</v>
@@ -1869,18 +1869,18 @@
       <c r="K20" s="51"/>
       <c r="L20" s="1"/>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="11">
         <v>18</v>
       </c>
-      <c r="B21" s="92" t="s">
+      <c r="B21" s="87" t="s">
         <v>49</v>
       </c>
       <c r="C21" s="38" t="s">
         <v>50</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>14</v>
@@ -1893,16 +1893,16 @@
       <c r="K21" s="54"/>
       <c r="L21" s="1"/>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="11">
         <v>19</v>
       </c>
-      <c r="B22" s="92"/>
+      <c r="B22" s="87"/>
       <c r="C22" s="38" t="s">
         <v>51</v>
       </c>
       <c r="D22" s="21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>14</v>
@@ -1911,11 +1911,11 @@
       <c r="H22" s="4"/>
       <c r="L22" s="1"/>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="11">
         <v>20</v>
       </c>
-      <c r="B23" s="92"/>
+      <c r="B23" s="87"/>
       <c r="C23" s="35" t="s">
         <v>52</v>
       </c>
@@ -1929,11 +1929,11 @@
       <c r="H23" s="4"/>
       <c r="L23" s="1"/>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="11">
         <v>21</v>
       </c>
-      <c r="B24" s="92"/>
+      <c r="B24" s="87"/>
       <c r="C24" s="35" t="s">
         <v>53</v>
       </c>
@@ -1947,16 +1947,16 @@
       <c r="H24" s="3"/>
       <c r="L24" s="1"/>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="11">
         <v>22</v>
       </c>
-      <c r="B25" s="92"/>
+      <c r="B25" s="87"/>
       <c r="C25" s="38" t="s">
         <v>54</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>14</v>
@@ -1965,18 +1965,18 @@
       <c r="H25" s="3"/>
       <c r="L25" s="1"/>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="11">
         <v>23</v>
       </c>
-      <c r="B26" s="79" t="s">
+      <c r="B26" s="88" t="s">
         <v>55</v>
       </c>
       <c r="C26" s="55" t="s">
         <v>56</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>14</v>
@@ -1985,11 +1985,11 @@
       <c r="H26" s="4"/>
       <c r="L26" s="1"/>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="11">
         <v>24</v>
       </c>
-      <c r="B27" s="79"/>
+      <c r="B27" s="88"/>
       <c r="C27" s="55" t="s">
         <v>57</v>
       </c>
@@ -2005,16 +2005,16 @@
       <c r="K27" s="6"/>
       <c r="L27" s="7"/>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="11">
         <v>25</v>
       </c>
-      <c r="B28" s="79"/>
+      <c r="B28" s="88"/>
       <c r="C28" s="55" t="s">
         <v>58</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>14</v>
@@ -2024,11 +2024,11 @@
       <c r="K28" s="6"/>
       <c r="L28" s="7"/>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="11">
         <v>26</v>
       </c>
-      <c r="B29" s="79"/>
+      <c r="B29" s="88"/>
       <c r="C29" s="55" t="s">
         <v>59</v>
       </c>
@@ -2057,11 +2057,11 @@
       <c r="AB29" s="6"/>
       <c r="AC29" s="6"/>
     </row>
-    <row r="30" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="11">
         <v>27</v>
       </c>
-      <c r="B30" s="79"/>
+      <c r="B30" s="88"/>
       <c r="C30" s="55" t="s">
         <v>60</v>
       </c>
@@ -2090,11 +2090,11 @@
       <c r="AB30" s="6"/>
       <c r="AC30" s="6"/>
     </row>
-    <row r="31" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="11">
         <v>28</v>
       </c>
-      <c r="B31" s="79"/>
+      <c r="B31" s="88"/>
       <c r="C31" s="55" t="s">
         <v>61</v>
       </c>
@@ -2123,11 +2123,11 @@
       <c r="AB31" s="6"/>
       <c r="AC31" s="6"/>
     </row>
-    <row r="32" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="11">
         <v>29</v>
       </c>
-      <c r="B32" s="79"/>
+      <c r="B32" s="88"/>
       <c r="C32" s="55" t="s">
         <v>62</v>
       </c>
@@ -2156,11 +2156,11 @@
       <c r="AB32" s="6"/>
       <c r="AC32" s="6"/>
     </row>
-    <row r="33" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="11">
         <v>30</v>
       </c>
-      <c r="B33" s="79"/>
+      <c r="B33" s="88"/>
       <c r="C33" s="55" t="s">
         <v>63</v>
       </c>
@@ -2190,11 +2190,11 @@
       <c r="AB33" s="6"/>
       <c r="AC33" s="6"/>
     </row>
-    <row r="34" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="11">
         <v>31</v>
       </c>
-      <c r="B34" s="79"/>
+      <c r="B34" s="88"/>
       <c r="C34" s="55" t="s">
         <v>64</v>
       </c>
@@ -2224,11 +2224,11 @@
       <c r="AB34" s="6"/>
       <c r="AC34" s="6"/>
     </row>
-    <row r="35" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="11">
         <v>32</v>
       </c>
-      <c r="B35" s="79"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="55" t="s">
         <v>65</v>
       </c>
@@ -2258,11 +2258,11 @@
       <c r="AB35" s="6"/>
       <c r="AC35" s="6"/>
     </row>
-    <row r="36" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="11">
         <v>33</v>
       </c>
-      <c r="B36" s="79"/>
+      <c r="B36" s="88"/>
       <c r="C36" s="55" t="s">
         <v>66</v>
       </c>
@@ -2292,11 +2292,11 @@
       <c r="AB36" s="6"/>
       <c r="AC36" s="6"/>
     </row>
-    <row r="37" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="11">
         <v>34</v>
       </c>
-      <c r="B37" s="79"/>
+      <c r="B37" s="88"/>
       <c r="C37" s="55" t="s">
         <v>67</v>
       </c>
@@ -2319,11 +2319,11 @@
       <c r="AB37" s="8"/>
       <c r="AC37" s="6"/>
     </row>
-    <row r="38" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="11">
         <v>35</v>
       </c>
-      <c r="B38" s="79"/>
+      <c r="B38" s="88"/>
       <c r="C38" s="55" t="s">
         <v>68</v>
       </c>
@@ -2346,11 +2346,11 @@
       <c r="AB38" s="66"/>
       <c r="AC38" s="6"/>
     </row>
-    <row r="39" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="11">
         <v>36</v>
       </c>
-      <c r="B39" s="79"/>
+      <c r="B39" s="88"/>
       <c r="C39" s="55" t="s">
         <v>69</v>
       </c>
@@ -2373,11 +2373,11 @@
       <c r="AB39" s="66"/>
       <c r="AC39" s="6"/>
     </row>
-    <row r="40" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="11">
         <v>37</v>
       </c>
-      <c r="B40" s="79"/>
+      <c r="B40" s="88"/>
       <c r="C40" s="55" t="s">
         <v>70</v>
       </c>
@@ -2400,11 +2400,11 @@
       <c r="AB40" s="6"/>
       <c r="AC40" s="6"/>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="11">
         <v>38</v>
       </c>
-      <c r="B41" s="79"/>
+      <c r="B41" s="88"/>
       <c r="C41" s="55" t="s">
         <v>71</v>
       </c>
@@ -2427,11 +2427,11 @@
       <c r="AB41" s="6"/>
       <c r="AC41" s="6"/>
     </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="11">
         <v>39</v>
       </c>
-      <c r="B42" s="79"/>
+      <c r="B42" s="88"/>
       <c r="C42" s="55" t="s">
         <v>72</v>
       </c>
@@ -2454,11 +2454,11 @@
       <c r="AB42" s="6"/>
       <c r="AC42" s="6"/>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="11">
         <v>40</v>
       </c>
-      <c r="B43" s="79"/>
+      <c r="B43" s="88"/>
       <c r="C43" s="55" t="s">
         <v>73</v>
       </c>
@@ -2481,11 +2481,11 @@
       <c r="AB43" s="6"/>
       <c r="AC43" s="6"/>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="11">
         <v>41</v>
       </c>
-      <c r="B44" s="79"/>
+      <c r="B44" s="88"/>
       <c r="C44" s="55" t="s">
         <v>74</v>
       </c>
@@ -2508,11 +2508,11 @@
       <c r="AB44" s="6"/>
       <c r="AC44" s="6"/>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="11">
         <v>42</v>
       </c>
-      <c r="B45" s="79"/>
+      <c r="B45" s="88"/>
       <c r="C45" s="55" t="s">
         <v>75</v>
       </c>
@@ -2535,11 +2535,11 @@
       <c r="AB45" s="6"/>
       <c r="AC45" s="6"/>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="11">
         <v>43</v>
       </c>
-      <c r="B46" s="79"/>
+      <c r="B46" s="88"/>
       <c r="C46" s="55" t="s">
         <v>76</v>
       </c>
@@ -2562,11 +2562,11 @@
       <c r="AB46" s="6"/>
       <c r="AC46" s="6"/>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="11">
         <v>44</v>
       </c>
-      <c r="B47" s="79"/>
+      <c r="B47" s="88"/>
       <c r="C47" s="55" t="s">
         <v>77</v>
       </c>
@@ -2589,11 +2589,11 @@
       <c r="AB47" s="6"/>
       <c r="AC47" s="6"/>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="11">
         <v>45</v>
       </c>
-      <c r="B48" s="79"/>
+      <c r="B48" s="88"/>
       <c r="C48" s="55" t="s">
         <v>78</v>
       </c>
@@ -2616,11 +2616,11 @@
       <c r="AB48" s="6"/>
       <c r="AC48" s="6"/>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="11">
         <v>46</v>
       </c>
-      <c r="B49" s="79"/>
+      <c r="B49" s="88"/>
       <c r="C49" s="55" t="s">
         <v>79</v>
       </c>
@@ -2643,16 +2643,16 @@
       <c r="AB49" s="6"/>
       <c r="AC49" s="6"/>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="11">
         <v>47</v>
       </c>
-      <c r="B50" s="79"/>
+      <c r="B50" s="88"/>
       <c r="C50" s="35" t="s">
         <v>80</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>14</v>
@@ -2670,16 +2670,16 @@
       <c r="AB50" s="6"/>
       <c r="AC50" s="6"/>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="11">
         <v>48</v>
       </c>
-      <c r="B51" s="79"/>
+      <c r="B51" s="88"/>
       <c r="C51" s="35" t="s">
         <v>81</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>14</v>
@@ -2697,16 +2697,16 @@
       <c r="AB51" s="6"/>
       <c r="AC51" s="6"/>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="11">
         <v>49</v>
       </c>
-      <c r="B52" s="79"/>
+      <c r="B52" s="88"/>
       <c r="C52" s="35" t="s">
         <v>82</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>14</v>
@@ -2724,11 +2724,11 @@
       <c r="AB52" s="6"/>
       <c r="AC52" s="6"/>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="11">
         <v>50</v>
       </c>
-      <c r="B53" s="80" t="s">
+      <c r="B53" s="89" t="s">
         <v>83</v>
       </c>
       <c r="C53" s="20" t="s">
@@ -2753,16 +2753,16 @@
       <c r="AB53" s="6"/>
       <c r="AC53" s="6"/>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="11">
         <v>51</v>
       </c>
-      <c r="B54" s="80"/>
+      <c r="B54" s="89"/>
       <c r="C54" s="20" t="s">
         <v>85</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>14</v>
@@ -2780,16 +2780,16 @@
       <c r="AB54" s="6"/>
       <c r="AC54" s="6"/>
     </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="11">
         <v>52</v>
       </c>
-      <c r="B55" s="80"/>
+      <c r="B55" s="89"/>
       <c r="C55" s="58" t="s">
         <v>86</v>
       </c>
       <c r="D55" s="21" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>14</v>
@@ -2809,16 +2809,16 @@
       <c r="AB55" s="6"/>
       <c r="AC55" s="6"/>
     </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="11">
         <v>53</v>
       </c>
-      <c r="B56" s="80"/>
+      <c r="B56" s="89"/>
       <c r="C56" s="58" t="s">
         <v>87</v>
       </c>
       <c r="D56" s="56" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>14</v>
@@ -2836,16 +2836,16 @@
       <c r="AB56" s="6"/>
       <c r="AC56" s="6"/>
     </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="11">
         <v>54</v>
       </c>
-      <c r="B57" s="80"/>
+      <c r="B57" s="89"/>
       <c r="C57" s="38" t="s">
         <v>88</v>
       </c>
       <c r="D57" s="21" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>14</v>
@@ -2863,16 +2863,16 @@
       <c r="AB57" s="6"/>
       <c r="AC57" s="6"/>
     </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="11">
         <v>55</v>
       </c>
-      <c r="B58" s="80"/>
+      <c r="B58" s="89"/>
       <c r="C58" s="58" t="s">
         <v>89</v>
       </c>
       <c r="D58" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>14</v>
@@ -2890,16 +2890,16 @@
       <c r="AB58" s="5"/>
       <c r="AC58" s="6"/>
     </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="11">
         <v>56</v>
       </c>
-      <c r="B59" s="80"/>
+      <c r="B59" s="89"/>
       <c r="C59" s="58" t="s">
         <v>90</v>
       </c>
       <c r="D59" s="21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>14</v>
@@ -2917,11 +2917,11 @@
       <c r="AB59" s="5"/>
       <c r="AC59" s="6"/>
     </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="11">
         <v>57</v>
       </c>
-      <c r="B60" s="80"/>
+      <c r="B60" s="89"/>
       <c r="C60" s="20" t="s">
         <v>91</v>
       </c>
@@ -2944,11 +2944,11 @@
       <c r="AB60" s="8"/>
       <c r="AC60" s="6"/>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="11">
         <v>58</v>
       </c>
-      <c r="B61" s="81" t="s">
+      <c r="B61" s="90" t="s">
         <v>92</v>
       </c>
       <c r="C61" s="58" t="s">
@@ -2973,11 +2973,11 @@
       <c r="AB61" s="8"/>
       <c r="AC61" s="6"/>
     </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="11">
         <v>59</v>
       </c>
-      <c r="B62" s="81"/>
+      <c r="B62" s="90"/>
       <c r="C62" s="58" t="s">
         <v>94</v>
       </c>
@@ -3000,11 +3000,11 @@
       <c r="AB62" s="5"/>
       <c r="AC62" s="6"/>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="11">
         <v>60</v>
       </c>
-      <c r="B63" s="81"/>
+      <c r="B63" s="90"/>
       <c r="C63" s="58" t="s">
         <v>95</v>
       </c>
@@ -3027,16 +3027,16 @@
       <c r="AB63" s="6"/>
       <c r="AC63" s="6"/>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="11">
         <v>61</v>
       </c>
-      <c r="B64" s="81"/>
+      <c r="B64" s="90"/>
       <c r="C64" s="58" t="s">
         <v>96</v>
       </c>
       <c r="D64" s="21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>14</v>
@@ -3054,11 +3054,11 @@
       <c r="AB64" s="6"/>
       <c r="AC64" s="6"/>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="11">
         <v>62</v>
       </c>
-      <c r="B65" s="81"/>
+      <c r="B65" s="90"/>
       <c r="C65" s="20" t="s">
         <v>97</v>
       </c>
@@ -3079,11 +3079,11 @@
       <c r="AB65" s="6"/>
       <c r="AC65" s="6"/>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="11">
         <v>63</v>
       </c>
-      <c r="B66" s="81"/>
+      <c r="B66" s="90"/>
       <c r="C66" s="20" t="s">
         <v>98</v>
       </c>
@@ -3092,11 +3092,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="11">
         <v>64</v>
       </c>
-      <c r="B67" s="81"/>
+      <c r="B67" s="90"/>
       <c r="C67" s="58" t="s">
         <v>99</v>
       </c>
@@ -3105,11 +3105,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="11">
         <v>65</v>
       </c>
-      <c r="B68" s="82" t="s">
+      <c r="B68" s="91" t="s">
         <v>100</v>
       </c>
       <c r="C68" s="60" t="s">
@@ -3120,11 +3120,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="11">
         <v>66</v>
       </c>
-      <c r="B69" s="82"/>
+      <c r="B69" s="91"/>
       <c r="C69" s="60" t="s">
         <v>102</v>
       </c>
@@ -3133,11 +3133,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="11">
         <v>67</v>
       </c>
-      <c r="B70" s="82"/>
+      <c r="B70" s="91"/>
       <c r="C70" s="60" t="s">
         <v>103</v>
       </c>
@@ -3146,11 +3146,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="11">
         <v>68</v>
       </c>
-      <c r="B71" s="82"/>
+      <c r="B71" s="91"/>
       <c r="C71" s="60" t="s">
         <v>104</v>
       </c>
@@ -3159,11 +3159,11 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:29" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="11">
         <v>69</v>
       </c>
-      <c r="B72" s="83"/>
+      <c r="B72" s="92"/>
       <c r="C72" s="61" t="s">
         <v>105</v>
       </c>
@@ -3174,16 +3174,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B26:B52"/>
+    <mergeCell ref="B53:B60"/>
+    <mergeCell ref="B61:B67"/>
+    <mergeCell ref="B68:B72"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="F2:K2"/>
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="B7:B10"/>
     <mergeCell ref="B11:B20"/>
     <mergeCell ref="B21:B25"/>
-    <mergeCell ref="B26:B52"/>
-    <mergeCell ref="B53:B60"/>
-    <mergeCell ref="B61:B67"/>
-    <mergeCell ref="B68:B72"/>
-    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3193,64 +3193,64 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:N413"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.89453125" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="18.6328125" style="23" customWidth="1"/>
-    <col min="2" max="2" width="21.81640625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="33.7265625" style="23" customWidth="1"/>
-    <col min="4" max="4" width="19.54296875" style="23" customWidth="1"/>
-    <col min="5" max="5" width="17.6328125" style="23" customWidth="1"/>
-    <col min="6" max="6" width="15.453125" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="17.6328125" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.6328125" style="23" customWidth="1"/>
-    <col min="10" max="10" width="11.26953125" style="23" customWidth="1"/>
-    <col min="11" max="16384" width="10.90625" style="23"/>
+    <col min="1" max="1" width="18.62890625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="21.7890625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="33.734375" style="23" customWidth="1"/>
+    <col min="4" max="4" width="19.5234375" style="23" customWidth="1"/>
+    <col min="5" max="5" width="17.62890625" style="23" customWidth="1"/>
+    <col min="6" max="6" width="15.47265625" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="17.62890625" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.62890625" style="23" customWidth="1"/>
+    <col min="10" max="10" width="11.26171875" style="23" customWidth="1"/>
+    <col min="11" max="16384" width="10.89453125" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="E1" s="64" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F1" s="64" t="s">
+        <v>134</v>
+      </c>
+      <c r="G1" s="64" t="s">
         <v>135</v>
       </c>
-      <c r="G1" s="64" t="s">
+      <c r="H1" s="64" t="s">
         <v>136</v>
       </c>
-      <c r="H1" s="64" t="s">
+      <c r="I1" s="64" t="s">
         <v>137</v>
       </c>
-      <c r="I1" s="64" t="s">
+      <c r="J1" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="J1" s="64" t="s">
+      <c r="K1" s="64" t="s">
         <v>139</v>
       </c>
-      <c r="K1" s="64" t="s">
+      <c r="L1" s="64" t="s">
         <v>140</v>
       </c>
-      <c r="L1" s="64" t="s">
+      <c r="M1" s="64" t="s">
         <v>141</v>
       </c>
-      <c r="M1" s="64" t="s">
+      <c r="N1" s="64" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="64" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B2" s="64" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D2" s="64" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E2" s="23">
         <v>181.07594439592833</v>
@@ -3283,18 +3283,18 @@
         <v>1553.3513427832988</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D3" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E3" s="23">
         <v>283.64826213093875</v>
@@ -3327,18 +3327,18 @@
         <v>2827.8352908756638</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D4" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E4" s="23">
         <v>427.80063797884975</v>
@@ -3371,18 +3371,18 @@
         <v>2865.3173513924062</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D5" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E5" s="23">
         <v>588.21950416125981</v>
@@ -3415,18 +3415,18 @@
         <v>2203.2512963604399</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D6" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" s="23">
         <v>108.27776395370699</v>
@@ -3459,18 +3459,18 @@
         <v>1142.3404537807594</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D7" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E7" s="23">
         <v>220.79584254983615</v>
@@ -3503,18 +3503,18 @@
         <v>1078.4594767310512</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D8" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E8" s="23">
         <v>295.98367670296824</v>
@@ -3547,18 +3547,18 @@
         <v>1345.7490705082437</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D9" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E9" s="23">
         <v>171.6297791738568</v>
@@ -3591,18 +3591,18 @@
         <v>1148.6865500628764</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D10" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E10" s="23">
         <v>102.65398324416381</v>
@@ -3635,18 +3635,18 @@
         <v>1067.1684856998738</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D11" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E11" s="23">
         <v>80.331528052507736</v>
@@ -3679,18 +3679,18 @@
         <v>901.77473591312105</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D12" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E12" s="23">
         <v>179.00178007581661</v>
@@ -3723,18 +3723,18 @@
         <v>1942.0197848892517</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D13" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E13" s="23">
         <v>318.09940225697795</v>
@@ -3767,18 +3767,18 @@
         <v>2951.5207175697055</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E14" s="23">
         <v>382.06114944509937</v>
@@ -3811,18 +3811,18 @@
         <v>2962.6139582737578</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E15" s="23">
         <v>51.535844168130872</v>
@@ -3855,18 +3855,18 @@
         <v>1126.6580217600988</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D16" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E16" s="23">
         <v>50.992273135967096</v>
@@ -3899,18 +3899,18 @@
         <v>1268.2910234485562</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E17" s="23">
         <v>208.37227316761781</v>
@@ -3943,18 +3943,18 @@
         <v>1346.3267505706601</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E18" s="23">
         <v>271.91661705494465</v>
@@ -3987,18 +3987,18 @@
         <v>1197.2520067975636</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E19" s="23">
         <v>250.75385323214076</v>
@@ -4031,18 +4031,18 @@
         <v>1166.4922729923769</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E20" s="23">
         <v>50.745410284313628</v>
@@ -4075,18 +4075,18 @@
         <v>849.65967289753416</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E21" s="23">
         <v>72.085628159642013</v>
@@ -4119,18 +4119,18 @@
         <v>1220.502062666962</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B22" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="D22" s="23" t="s">
         <v>124</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>125</v>
       </c>
       <c r="E22" s="23">
         <v>0</v>
@@ -4163,18 +4163,18 @@
         <v>1157.0880612216672</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E23" s="23">
         <v>137.13547990735523</v>
@@ -4207,18 +4207,18 @@
         <v>2090.6594855629082</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E24" s="23">
         <v>139.90279764167204</v>
@@ -4251,18 +4251,18 @@
         <v>1681.8702461772496</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E25" s="23">
         <v>51.300778869359235</v>
@@ -4295,18 +4295,18 @@
         <v>1419.8331398204532</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E26" s="23">
         <v>1.6725927366628295</v>
@@ -4339,18 +4339,18 @@
         <v>1300.3148584974915</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E27" s="23">
         <v>9.211239523600792</v>
@@ -4383,18 +4383,18 @@
         <v>1429.6424563027035</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E28" s="23">
         <v>41.943101306587359</v>
@@ -4427,18 +4427,18 @@
         <v>1120.7294515508736</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E29" s="23">
         <v>110.98215778739326</v>
@@ -4471,18 +4471,18 @@
         <v>1427.986812892171</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E30" s="23">
         <v>19.780720091792915</v>
@@ -4515,18 +4515,18 @@
         <v>1549.9473307264939</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E31" s="23">
         <v>24.331981841340912</v>
@@ -4559,18 +4559,18 @@
         <v>1054.5588636106129</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E32" s="23">
         <v>0</v>
@@ -4603,18 +4603,18 @@
         <v>808.47288350687518</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E33" s="23">
         <v>0</v>
@@ -4647,18 +4647,18 @@
         <v>1238.171609406932</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E34" s="23">
         <v>0</v>
@@ -4691,18 +4691,18 @@
         <v>1249.0922024333011</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E35" s="23">
         <v>0</v>
@@ -4735,18 +4735,18 @@
         <v>874.95273618947988</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E36" s="23">
         <v>0</v>
@@ -4779,18 +4779,18 @@
         <v>395.46809310751973</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E37" s="23">
         <v>0</v>
@@ -4823,18 +4823,18 @@
         <v>453.45632682855876</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E38" s="23">
         <v>0</v>
@@ -4867,18 +4867,18 @@
         <v>515.26078716547352</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E39" s="23">
         <v>0</v>
@@ -4911,18 +4911,18 @@
         <v>427.91111808720723</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E40" s="23">
         <v>0</v>
@@ -4955,18 +4955,18 @@
         <v>473.42010247487826</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E41" s="23">
         <v>0</v>
@@ -4999,18 +4999,18 @@
         <v>372.41018226460181</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E42" s="23">
         <v>0</v>
@@ -5043,18 +5043,18 @@
         <v>1147.1939019466033</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E43" s="23">
         <v>0</v>
@@ -5087,18 +5087,18 @@
         <v>1561.4810565478488</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E44" s="23">
         <v>0</v>
@@ -5131,18 +5131,18 @@
         <v>1058.1754333520967</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E45" s="23">
         <v>0</v>
@@ -5175,18 +5175,18 @@
         <v>597.3434620418011</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E46" s="23">
         <v>0</v>
@@ -5219,18 +5219,18 @@
         <v>573.27831350361726</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E47" s="74">
         <v>0</v>
@@ -5263,18 +5263,18 @@
         <v>590.04931963546881</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E48" s="74">
         <v>0</v>
@@ -5307,18 +5307,18 @@
         <v>419.97078034421702</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E49" s="74">
         <v>0</v>
@@ -5351,18 +5351,18 @@
         <v>452.67530224055832</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E50" s="74">
         <v>0</v>
@@ -5395,18 +5395,18 @@
         <v>364.71213463894219</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E51" s="74">
         <v>0</v>
@@ -5439,18 +5439,18 @@
         <v>655.06087581608017</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B52" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="D52" s="23" t="s">
         <v>124</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>125</v>
       </c>
       <c r="E52" s="74">
         <v>0</v>
@@ -5483,18 +5483,18 @@
         <v>744.40600294186379</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E53" s="74">
         <v>0</v>
@@ -5527,18 +5527,18 @@
         <v>1217.5153954393588</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E54" s="74">
         <v>7.6438830133680131</v>
@@ -5571,18 +5571,18 @@
         <v>993.96198196544606</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E55" s="74">
         <v>0</v>
@@ -5615,18 +5615,18 @@
         <v>1014.6946979048595</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E56" s="74">
         <v>0</v>
@@ -5659,18 +5659,18 @@
         <v>898.30993398900512</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E57" s="74">
         <v>0</v>
@@ -5703,18 +5703,18 @@
         <v>810.33806533396751</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E58" s="74">
         <v>0</v>
@@ -5747,18 +5747,18 @@
         <v>647.05560964521874</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E59" s="74">
         <v>0</v>
@@ -5791,18 +5791,18 @@
         <v>786.13259830986328</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E60" s="74">
         <v>0</v>
@@ -5835,18 +5835,18 @@
         <v>995.10661230208495</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E61" s="74">
         <v>0</v>
@@ -5879,18 +5879,18 @@
         <v>633.9458622417892</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E62" s="74">
         <v>181.07594439592833</v>
@@ -5923,18 +5923,18 @@
         <v>744.87845927642229</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E63" s="74">
         <v>283.64826213093875</v>
@@ -5967,18 +5967,18 @@
         <v>1589.6636814687315</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E64" s="74">
         <v>427.80063797884975</v>
@@ -6011,18 +6011,18 @@
         <v>1616.2251489591008</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E65" s="74">
         <v>588.21950416125981</v>
@@ -6055,18 +6055,18 @@
         <v>1328.2985601709609</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E66" s="74">
         <v>108.27776395370739</v>
@@ -6099,18 +6099,18 @@
         <v>746.87236067323374</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B67" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E67" s="74">
         <v>220.79584254983615</v>
@@ -6143,18 +6143,18 @@
         <v>625.00314990249285</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E68" s="74">
         <v>295.98367670296824</v>
@@ -6187,18 +6187,18 @@
         <v>830.48828334276834</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B69" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E69" s="74">
         <v>171.6297791738568</v>
@@ -6231,18 +6231,18 @@
         <v>720.77543197566922</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E70" s="74">
         <v>102.65398324416381</v>
@@ -6275,18 +6275,18 @@
         <v>593.748383224995</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E71" s="74">
         <v>80.331528052507736</v>
@@ -6319,18 +6319,18 @@
         <v>529.36455364851838</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E72" s="74">
         <v>179.00178007581661</v>
@@ -6363,18 +6363,18 @@
         <v>794.82588294264883</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B73" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E73" s="74">
         <v>318.09940225697795</v>
@@ -6407,18 +6407,18 @@
         <v>1390.0396610218518</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B74" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E74" s="74">
         <v>382.06114944509937</v>
@@ -6451,18 +6451,18 @@
         <v>1904.438524921658</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E75" s="74">
         <v>51.535844168130872</v>
@@ -6495,18 +6495,18 @@
         <v>529.31455971829701</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E76" s="74">
         <v>50.992273135967096</v>
@@ -6539,18 +6539,18 @@
         <v>695.012709944942</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E77" s="74">
         <v>208.37227316761781</v>
@@ -6583,18 +6583,18 @@
         <v>756.27743093519143</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E78" s="74">
         <v>271.91661705494465</v>
@@ -6627,18 +6627,18 @@
         <v>777.28122645334804</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E79" s="74">
         <v>250.75385323214076</v>
@@ -6671,18 +6671,18 @@
         <v>713.81697075182069</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E80" s="74">
         <v>50.745410284313628</v>
@@ -6715,18 +6715,18 @@
         <v>484.94753825859198</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E81" s="74">
         <v>72.085628159642013</v>
@@ -6759,18 +6759,18 @@
         <v>565.44118685088188</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B82" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="D82" s="23" t="s">
         <v>124</v>
-      </c>
-      <c r="C82" s="23" t="s">
-        <v>164</v>
-      </c>
-      <c r="D82" s="23" t="s">
-        <v>125</v>
       </c>
       <c r="E82" s="74">
         <v>0</v>
@@ -6803,18 +6803,18 @@
         <v>412.68205827980404</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E83" s="74">
         <v>137.13547990735523</v>
@@ -6847,18 +6847,18 @@
         <v>873.1440901235419</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E84" s="74">
         <v>132.25891462830393</v>
@@ -6891,18 +6891,18 @@
         <v>687.90826421180429</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B85" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C85" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D85" s="23" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E85" s="74">
         <v>51.300778869359235</v>
@@ -6935,18 +6935,18 @@
         <v>405.13844191559315</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B86" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C86" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E86" s="74">
         <v>1.6725927366628295</v>
@@ -6979,18 +6979,18 @@
         <v>402.00492450848668</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B87" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C87" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E87" s="74">
         <v>9.211239523600792</v>
@@ -7023,18 +7023,18 @@
         <v>619.30439096873647</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B88" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C88" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E88" s="74">
         <v>41.943101306587359</v>
@@ -7067,18 +7067,18 @@
         <v>473.67384190565497</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B89" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C89" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E89" s="74">
         <v>110.98215778739326</v>
@@ -7111,18 +7111,18 @@
         <v>641.85421458230769</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B90" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C90" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E90" s="74">
         <v>19.780720091792915</v>
@@ -7155,18 +7155,18 @@
         <v>554.84071842440892</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="64" t="s">
         <v>120</v>
       </c>
       <c r="B91" s="23" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C91" s="23" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E91" s="74">
         <v>24.331981841340912</v>
@@ -7199,2254 +7199,2254 @@
         <v>420.61300136882352</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="74"/>
       <c r="B92" s="74"/>
       <c r="C92" s="74"/>
       <c r="E92" s="74"/>
       <c r="F92" s="74"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="74"/>
       <c r="B93" s="74"/>
       <c r="C93" s="74"/>
       <c r="E93" s="74"/>
       <c r="F93" s="74"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="74"/>
       <c r="B94" s="74"/>
       <c r="C94" s="74"/>
       <c r="E94" s="74"/>
       <c r="F94" s="74"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="74"/>
       <c r="B95" s="74"/>
       <c r="C95" s="74"/>
       <c r="E95" s="74"/>
       <c r="F95" s="74"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="74"/>
       <c r="B96" s="74"/>
       <c r="C96" s="74"/>
       <c r="E96" s="74"/>
       <c r="F96" s="74"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="74"/>
       <c r="B97" s="74"/>
       <c r="C97" s="74"/>
       <c r="E97" s="74"/>
       <c r="F97" s="74"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="74"/>
       <c r="B98" s="74"/>
       <c r="C98" s="74"/>
       <c r="E98" s="74"/>
       <c r="F98" s="74"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="74"/>
       <c r="B99" s="74"/>
       <c r="C99" s="74"/>
       <c r="E99" s="74"/>
       <c r="F99" s="74"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="74"/>
       <c r="B100" s="74"/>
       <c r="C100" s="74"/>
       <c r="E100" s="74"/>
       <c r="F100" s="74"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="74"/>
       <c r="B101" s="74"/>
       <c r="C101" s="74"/>
       <c r="E101" s="74"/>
       <c r="F101" s="74"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="74"/>
       <c r="B102" s="74"/>
       <c r="C102" s="74"/>
       <c r="E102" s="74"/>
       <c r="F102" s="74"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="74"/>
       <c r="B103" s="74"/>
       <c r="C103" s="74"/>
       <c r="E103" s="74"/>
       <c r="F103" s="74"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="74"/>
       <c r="B104" s="74"/>
       <c r="C104" s="74"/>
       <c r="E104" s="74"/>
       <c r="F104" s="74"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="74"/>
       <c r="B105" s="74"/>
       <c r="C105" s="74"/>
       <c r="E105" s="74"/>
       <c r="F105" s="74"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="74"/>
       <c r="B106" s="74"/>
       <c r="C106" s="74"/>
       <c r="E106" s="74"/>
       <c r="F106" s="74"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="74"/>
       <c r="B107" s="74"/>
       <c r="C107" s="74"/>
       <c r="E107" s="74"/>
       <c r="F107" s="74"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="74"/>
       <c r="B108" s="74"/>
       <c r="C108" s="74"/>
       <c r="E108" s="74"/>
       <c r="F108" s="74"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="74"/>
       <c r="B109" s="74"/>
       <c r="C109" s="74"/>
       <c r="E109" s="74"/>
       <c r="F109" s="74"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="74"/>
       <c r="B110" s="74"/>
       <c r="C110" s="74"/>
       <c r="E110" s="74"/>
       <c r="F110" s="74"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="74"/>
       <c r="B111" s="74"/>
       <c r="C111" s="74"/>
       <c r="E111" s="74"/>
       <c r="F111" s="74"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="74"/>
       <c r="B112" s="74"/>
       <c r="C112" s="74"/>
       <c r="E112" s="74"/>
       <c r="F112" s="74"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="74"/>
       <c r="B113" s="74"/>
       <c r="C113" s="74"/>
       <c r="E113" s="74"/>
       <c r="F113" s="74"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="74"/>
       <c r="B114" s="74"/>
       <c r="C114" s="74"/>
       <c r="E114" s="74"/>
       <c r="F114" s="74"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="74"/>
       <c r="B115" s="74"/>
       <c r="C115" s="74"/>
       <c r="E115" s="74"/>
       <c r="F115" s="74"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="74"/>
       <c r="B116" s="74"/>
       <c r="C116" s="74"/>
       <c r="E116" s="74"/>
       <c r="F116" s="74"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="74"/>
       <c r="B117" s="74"/>
       <c r="C117" s="74"/>
       <c r="E117" s="74"/>
       <c r="F117" s="74"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="74"/>
       <c r="B118" s="74"/>
       <c r="C118" s="74"/>
       <c r="E118" s="74"/>
       <c r="F118" s="74"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="74"/>
       <c r="B119" s="74"/>
       <c r="C119" s="74"/>
       <c r="E119" s="74"/>
       <c r="F119" s="74"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="74"/>
       <c r="B120" s="74"/>
       <c r="C120" s="74"/>
       <c r="E120" s="74"/>
       <c r="F120" s="74"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="74"/>
       <c r="B121" s="74"/>
       <c r="C121" s="74"/>
       <c r="E121" s="74"/>
       <c r="F121" s="74"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="74"/>
       <c r="B122" s="74"/>
       <c r="C122" s="74"/>
       <c r="E122" s="74"/>
       <c r="F122" s="74"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="74"/>
       <c r="B123" s="74"/>
       <c r="C123" s="74"/>
       <c r="E123" s="74"/>
       <c r="F123" s="74"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="74"/>
       <c r="B124" s="74"/>
       <c r="C124" s="74"/>
       <c r="E124" s="74"/>
       <c r="F124" s="74"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="74"/>
       <c r="B125" s="74"/>
       <c r="C125" s="74"/>
       <c r="E125" s="74"/>
       <c r="F125" s="74"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="74"/>
       <c r="B126" s="74"/>
       <c r="C126" s="74"/>
       <c r="E126" s="74"/>
       <c r="F126" s="74"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="74"/>
       <c r="B127" s="74"/>
       <c r="C127" s="74"/>
       <c r="E127" s="74"/>
       <c r="F127" s="74"/>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="74"/>
       <c r="B128" s="74"/>
       <c r="C128" s="74"/>
       <c r="E128" s="74"/>
       <c r="F128" s="74"/>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="74"/>
       <c r="B129" s="74"/>
       <c r="C129" s="74"/>
       <c r="E129" s="74"/>
       <c r="F129" s="74"/>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" s="74"/>
       <c r="B130" s="74"/>
       <c r="C130" s="74"/>
       <c r="E130" s="74"/>
       <c r="F130" s="74"/>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="74"/>
       <c r="B131" s="74"/>
       <c r="C131" s="74"/>
       <c r="E131" s="74"/>
       <c r="F131" s="74"/>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="74"/>
       <c r="B132" s="74"/>
       <c r="C132" s="74"/>
       <c r="E132" s="74"/>
       <c r="F132" s="74"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="74"/>
       <c r="B133" s="74"/>
       <c r="C133" s="74"/>
       <c r="E133" s="74"/>
       <c r="F133" s="74"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="74"/>
       <c r="B134" s="74"/>
       <c r="C134" s="74"/>
       <c r="E134" s="74"/>
       <c r="F134" s="74"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="74"/>
       <c r="B135" s="74"/>
       <c r="C135" s="74"/>
       <c r="E135" s="74"/>
       <c r="F135" s="74"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="74"/>
       <c r="B136" s="74"/>
       <c r="C136" s="74"/>
       <c r="E136" s="74"/>
       <c r="F136" s="74"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="74"/>
       <c r="B137" s="74"/>
       <c r="C137" s="74"/>
       <c r="E137" s="74"/>
       <c r="F137" s="74"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="74"/>
       <c r="B138" s="74"/>
       <c r="C138" s="74"/>
       <c r="E138" s="74"/>
       <c r="F138" s="74"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="74"/>
       <c r="B139" s="74"/>
       <c r="C139" s="74"/>
       <c r="E139" s="74"/>
       <c r="F139" s="74"/>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="74"/>
       <c r="B140" s="74"/>
       <c r="C140" s="74"/>
       <c r="E140" s="74"/>
       <c r="F140" s="74"/>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="74"/>
       <c r="B141" s="74"/>
       <c r="C141" s="74"/>
       <c r="E141" s="74"/>
       <c r="F141" s="74"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="74"/>
       <c r="B142" s="74"/>
       <c r="C142" s="74"/>
       <c r="E142" s="74"/>
       <c r="F142" s="74"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="74"/>
       <c r="B143" s="74"/>
       <c r="C143" s="74"/>
       <c r="E143" s="74"/>
       <c r="F143" s="74"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="74"/>
       <c r="B144" s="74"/>
       <c r="C144" s="74"/>
       <c r="E144" s="74"/>
       <c r="F144" s="74"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="74"/>
       <c r="B145" s="74"/>
       <c r="C145" s="74"/>
       <c r="E145" s="74"/>
       <c r="F145" s="74"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="74"/>
       <c r="B146" s="74"/>
       <c r="C146" s="74"/>
       <c r="E146" s="74"/>
       <c r="F146" s="74"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="74"/>
       <c r="B147" s="74"/>
       <c r="C147" s="74"/>
       <c r="E147" s="74"/>
       <c r="F147" s="74"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="74"/>
       <c r="B148" s="74"/>
       <c r="C148" s="74"/>
       <c r="E148" s="74"/>
       <c r="F148" s="74"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="74"/>
       <c r="B149" s="74"/>
       <c r="C149" s="74"/>
       <c r="E149" s="74"/>
       <c r="F149" s="74"/>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="74"/>
       <c r="B150" s="74"/>
       <c r="C150" s="74"/>
       <c r="E150" s="74"/>
       <c r="F150" s="74"/>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="74"/>
       <c r="B151" s="74"/>
       <c r="C151" s="74"/>
       <c r="E151" s="74"/>
       <c r="F151" s="74"/>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="74"/>
       <c r="B152" s="74"/>
       <c r="C152" s="74"/>
       <c r="E152" s="74"/>
       <c r="F152" s="74"/>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="74"/>
       <c r="B153" s="74"/>
       <c r="C153" s="74"/>
       <c r="E153" s="74"/>
       <c r="F153" s="74"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="74"/>
       <c r="B154" s="74"/>
       <c r="C154" s="74"/>
       <c r="E154" s="74"/>
       <c r="F154" s="74"/>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="74"/>
       <c r="B155" s="74"/>
       <c r="C155" s="74"/>
       <c r="E155" s="74"/>
       <c r="F155" s="74"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="74"/>
       <c r="B156" s="74"/>
       <c r="C156" s="74"/>
       <c r="E156" s="74"/>
       <c r="F156" s="74"/>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="74"/>
       <c r="B157" s="74"/>
       <c r="C157" s="74"/>
       <c r="E157" s="74"/>
       <c r="F157" s="74"/>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="74"/>
       <c r="B158" s="74"/>
       <c r="C158" s="74"/>
       <c r="E158" s="74"/>
       <c r="F158" s="74"/>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="74"/>
       <c r="B159" s="74"/>
       <c r="C159" s="74"/>
       <c r="E159" s="74"/>
       <c r="F159" s="74"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" s="74"/>
       <c r="B160" s="74"/>
       <c r="C160" s="74"/>
       <c r="E160" s="74"/>
       <c r="F160" s="74"/>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="74"/>
       <c r="B161" s="74"/>
       <c r="C161" s="74"/>
       <c r="E161" s="74"/>
       <c r="F161" s="74"/>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="74"/>
       <c r="B162" s="74"/>
       <c r="C162" s="74"/>
       <c r="E162" s="74"/>
       <c r="F162" s="74"/>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" s="74"/>
       <c r="B163" s="74"/>
       <c r="C163" s="74"/>
       <c r="E163" s="74"/>
       <c r="F163" s="74"/>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="74"/>
       <c r="B164" s="74"/>
       <c r="C164" s="74"/>
       <c r="E164" s="74"/>
       <c r="F164" s="74"/>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="74"/>
       <c r="B165" s="74"/>
       <c r="C165" s="74"/>
       <c r="E165" s="74"/>
       <c r="F165" s="74"/>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="74"/>
       <c r="B166" s="74"/>
       <c r="C166" s="74"/>
       <c r="E166" s="74"/>
       <c r="F166" s="74"/>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="74"/>
       <c r="B167" s="74"/>
       <c r="C167" s="74"/>
       <c r="E167" s="74"/>
       <c r="F167" s="74"/>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="74"/>
       <c r="B168" s="74"/>
       <c r="C168" s="74"/>
       <c r="E168" s="74"/>
       <c r="F168" s="74"/>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="74"/>
       <c r="B169" s="74"/>
       <c r="C169" s="74"/>
       <c r="E169" s="74"/>
       <c r="F169" s="74"/>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="74"/>
       <c r="B170" s="74"/>
       <c r="C170" s="74"/>
       <c r="E170" s="74"/>
       <c r="F170" s="74"/>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="74"/>
       <c r="B171" s="74"/>
       <c r="C171" s="74"/>
       <c r="E171" s="74"/>
       <c r="F171" s="74"/>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="74"/>
       <c r="B172" s="74"/>
       <c r="C172" s="74"/>
       <c r="E172" s="74"/>
       <c r="F172" s="74"/>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="74"/>
       <c r="B173" s="74"/>
       <c r="C173" s="74"/>
       <c r="E173" s="74"/>
       <c r="F173" s="74"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="74"/>
       <c r="B174" s="74"/>
       <c r="C174" s="74"/>
       <c r="E174" s="74"/>
       <c r="F174" s="74"/>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="74"/>
       <c r="B175" s="74"/>
       <c r="C175" s="74"/>
       <c r="E175" s="74"/>
       <c r="F175" s="74"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="74"/>
       <c r="B176" s="74"/>
       <c r="C176" s="74"/>
       <c r="E176" s="74"/>
       <c r="F176" s="74"/>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="74"/>
       <c r="B177" s="74"/>
       <c r="C177" s="74"/>
       <c r="E177" s="74"/>
       <c r="F177" s="74"/>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="74"/>
       <c r="B178" s="74"/>
       <c r="C178" s="74"/>
       <c r="E178" s="74"/>
       <c r="F178" s="74"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="74"/>
       <c r="B179" s="74"/>
       <c r="C179" s="74"/>
       <c r="E179" s="74"/>
       <c r="F179" s="74"/>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="74"/>
       <c r="B180" s="74"/>
       <c r="C180" s="74"/>
       <c r="E180" s="74"/>
       <c r="F180" s="74"/>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="74"/>
       <c r="B181" s="74"/>
       <c r="C181" s="74"/>
       <c r="E181" s="74"/>
       <c r="F181" s="74"/>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="74"/>
       <c r="B182" s="74"/>
       <c r="C182" s="74"/>
       <c r="E182" s="74"/>
       <c r="F182" s="74"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="74"/>
       <c r="B183" s="74"/>
       <c r="C183" s="74"/>
       <c r="E183" s="74"/>
       <c r="F183" s="74"/>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="74"/>
       <c r="B184" s="74"/>
       <c r="C184" s="74"/>
       <c r="E184" s="74"/>
       <c r="F184" s="74"/>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="74"/>
       <c r="B185" s="74"/>
       <c r="C185" s="74"/>
       <c r="E185" s="74"/>
       <c r="F185" s="74"/>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="74"/>
       <c r="B186" s="74"/>
       <c r="C186" s="74"/>
       <c r="E186" s="74"/>
       <c r="F186" s="74"/>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="74"/>
       <c r="B187" s="74"/>
       <c r="C187" s="74"/>
       <c r="E187" s="74"/>
       <c r="F187" s="74"/>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="74"/>
       <c r="B188" s="74"/>
       <c r="C188" s="74"/>
       <c r="E188" s="74"/>
       <c r="F188" s="74"/>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="74"/>
       <c r="B189" s="74"/>
       <c r="C189" s="74"/>
       <c r="E189" s="74"/>
       <c r="F189" s="74"/>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="74"/>
       <c r="B190" s="74"/>
       <c r="C190" s="74"/>
       <c r="E190" s="74"/>
       <c r="F190" s="74"/>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="74"/>
       <c r="B191" s="74"/>
       <c r="C191" s="74"/>
       <c r="E191" s="74"/>
       <c r="F191" s="74"/>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="74"/>
       <c r="B192" s="74"/>
       <c r="C192" s="74"/>
       <c r="E192" s="74"/>
       <c r="F192" s="74"/>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="74"/>
       <c r="B193" s="74"/>
       <c r="C193" s="74"/>
       <c r="E193" s="74"/>
       <c r="F193" s="74"/>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="74"/>
       <c r="B194" s="74"/>
       <c r="C194" s="74"/>
       <c r="E194" s="74"/>
       <c r="F194" s="74"/>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="74"/>
       <c r="B195" s="74"/>
       <c r="C195" s="74"/>
       <c r="E195" s="74"/>
       <c r="F195" s="74"/>
     </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="74"/>
       <c r="B196" s="74"/>
       <c r="C196" s="74"/>
       <c r="E196" s="74"/>
       <c r="F196" s="74"/>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="74"/>
       <c r="B197" s="74"/>
       <c r="C197" s="74"/>
       <c r="E197" s="74"/>
       <c r="F197" s="74"/>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="74"/>
       <c r="B198" s="74"/>
       <c r="C198" s="74"/>
       <c r="E198" s="74"/>
       <c r="F198" s="74"/>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="74"/>
       <c r="B199" s="74"/>
       <c r="C199" s="74"/>
       <c r="E199" s="74"/>
       <c r="F199" s="74"/>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="74"/>
       <c r="B200" s="74"/>
       <c r="C200" s="74"/>
       <c r="E200" s="74"/>
       <c r="F200" s="74"/>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="74"/>
       <c r="B201" s="74"/>
       <c r="C201" s="74"/>
       <c r="E201" s="74"/>
       <c r="F201" s="74"/>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="74"/>
       <c r="B202" s="74"/>
       <c r="C202" s="74"/>
       <c r="E202" s="74"/>
       <c r="F202" s="74"/>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="74"/>
       <c r="B203" s="74"/>
       <c r="C203" s="74"/>
       <c r="E203" s="74"/>
       <c r="F203" s="74"/>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="74"/>
       <c r="B204" s="74"/>
       <c r="C204" s="74"/>
       <c r="E204" s="74"/>
       <c r="F204" s="74"/>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="74"/>
       <c r="B205" s="74"/>
       <c r="C205" s="74"/>
       <c r="E205" s="74"/>
       <c r="F205" s="74"/>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="74"/>
       <c r="B206" s="74"/>
       <c r="C206" s="74"/>
       <c r="E206" s="74"/>
       <c r="F206" s="74"/>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="74"/>
       <c r="B207" s="74"/>
       <c r="C207" s="74"/>
       <c r="E207" s="74"/>
       <c r="F207" s="74"/>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="74"/>
       <c r="B208" s="74"/>
       <c r="C208" s="74"/>
       <c r="E208" s="74"/>
       <c r="F208" s="74"/>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="74"/>
       <c r="B209" s="74"/>
       <c r="C209" s="74"/>
       <c r="E209" s="74"/>
       <c r="F209" s="74"/>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="74"/>
       <c r="B210" s="74"/>
       <c r="C210" s="74"/>
       <c r="E210" s="74"/>
       <c r="F210" s="74"/>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="74"/>
       <c r="B211" s="74"/>
       <c r="C211" s="74"/>
       <c r="E211" s="74"/>
       <c r="F211" s="74"/>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="74"/>
       <c r="B212" s="74"/>
       <c r="C212" s="74"/>
       <c r="E212" s="74"/>
       <c r="F212" s="74"/>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="74"/>
       <c r="B213" s="74"/>
       <c r="C213" s="74"/>
       <c r="E213" s="74"/>
       <c r="F213" s="74"/>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="74"/>
       <c r="B214" s="74"/>
       <c r="C214" s="74"/>
       <c r="E214" s="74"/>
       <c r="F214" s="74"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="74"/>
       <c r="B215" s="74"/>
       <c r="C215" s="74"/>
       <c r="E215" s="74"/>
       <c r="F215" s="74"/>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="74"/>
       <c r="B216" s="74"/>
       <c r="C216" s="74"/>
       <c r="E216" s="74"/>
       <c r="F216" s="74"/>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="74"/>
       <c r="B217" s="74"/>
       <c r="C217" s="74"/>
       <c r="E217" s="74"/>
       <c r="F217" s="74"/>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="74"/>
       <c r="B218" s="74"/>
       <c r="C218" s="74"/>
       <c r="E218" s="74"/>
       <c r="F218" s="74"/>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="74"/>
       <c r="B219" s="74"/>
       <c r="C219" s="74"/>
       <c r="E219" s="74"/>
       <c r="F219" s="74"/>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="74"/>
       <c r="B220" s="74"/>
       <c r="C220" s="74"/>
       <c r="E220" s="74"/>
       <c r="F220" s="74"/>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="74"/>
       <c r="B221" s="74"/>
       <c r="C221" s="74"/>
       <c r="E221" s="74"/>
       <c r="F221" s="74"/>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="74"/>
       <c r="B222" s="74"/>
       <c r="C222" s="74"/>
       <c r="E222" s="74"/>
       <c r="F222" s="74"/>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="74"/>
       <c r="B223" s="74"/>
       <c r="C223" s="74"/>
       <c r="E223" s="74"/>
       <c r="F223" s="74"/>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="74"/>
       <c r="B224" s="74"/>
       <c r="C224" s="74"/>
       <c r="E224" s="74"/>
       <c r="F224" s="74"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="74"/>
       <c r="B225" s="74"/>
       <c r="C225" s="74"/>
       <c r="E225" s="74"/>
       <c r="F225" s="74"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="74"/>
       <c r="B226" s="74"/>
       <c r="C226" s="74"/>
       <c r="E226" s="74"/>
       <c r="F226" s="74"/>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="74"/>
       <c r="B227" s="74"/>
       <c r="C227" s="74"/>
       <c r="E227" s="74"/>
       <c r="F227" s="74"/>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="74"/>
       <c r="B228" s="74"/>
       <c r="C228" s="74"/>
       <c r="E228" s="74"/>
       <c r="F228" s="74"/>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="74"/>
       <c r="B229" s="74"/>
       <c r="C229" s="74"/>
       <c r="E229" s="74"/>
       <c r="F229" s="74"/>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="74"/>
       <c r="B230" s="74"/>
       <c r="C230" s="74"/>
       <c r="E230" s="74"/>
       <c r="F230" s="74"/>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="74"/>
       <c r="B231" s="74"/>
       <c r="C231" s="74"/>
       <c r="E231" s="74"/>
       <c r="F231" s="74"/>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="74"/>
       <c r="B232" s="74"/>
       <c r="C232" s="74"/>
       <c r="E232" s="74"/>
       <c r="F232" s="74"/>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="74"/>
       <c r="B233" s="74"/>
       <c r="C233" s="74"/>
       <c r="E233" s="74"/>
       <c r="F233" s="74"/>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="74"/>
       <c r="B234" s="74"/>
       <c r="C234" s="74"/>
       <c r="E234" s="74"/>
       <c r="F234" s="74"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="74"/>
       <c r="B235" s="74"/>
       <c r="C235" s="74"/>
       <c r="E235" s="74"/>
       <c r="F235" s="74"/>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="74"/>
       <c r="B236" s="74"/>
       <c r="C236" s="74"/>
       <c r="E236" s="74"/>
       <c r="F236" s="74"/>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="74"/>
       <c r="B237" s="74"/>
       <c r="C237" s="74"/>
       <c r="E237" s="74"/>
       <c r="F237" s="74"/>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="74"/>
       <c r="B238" s="74"/>
       <c r="C238" s="74"/>
       <c r="E238" s="74"/>
       <c r="F238" s="74"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" s="74"/>
       <c r="B239" s="74"/>
       <c r="C239" s="74"/>
       <c r="E239" s="74"/>
       <c r="F239" s="74"/>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="74"/>
       <c r="B240" s="74"/>
       <c r="C240" s="74"/>
       <c r="E240" s="74"/>
       <c r="F240" s="74"/>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="74"/>
       <c r="B241" s="74"/>
       <c r="C241" s="74"/>
       <c r="E241" s="74"/>
       <c r="F241" s="74"/>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="74"/>
       <c r="B242" s="74"/>
       <c r="C242" s="74"/>
       <c r="E242" s="74"/>
       <c r="F242" s="74"/>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="74"/>
       <c r="B243" s="74"/>
       <c r="C243" s="74"/>
       <c r="E243" s="74"/>
       <c r="F243" s="74"/>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="74"/>
       <c r="B244" s="74"/>
       <c r="C244" s="74"/>
       <c r="E244" s="74"/>
       <c r="F244" s="74"/>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" s="74"/>
       <c r="B245" s="74"/>
       <c r="C245" s="74"/>
       <c r="E245" s="74"/>
       <c r="F245" s="74"/>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="74"/>
       <c r="B246" s="74"/>
       <c r="C246" s="74"/>
       <c r="E246" s="74"/>
       <c r="F246" s="74"/>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" s="74"/>
       <c r="B247" s="74"/>
       <c r="C247" s="74"/>
       <c r="E247" s="74"/>
       <c r="F247" s="74"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="74"/>
       <c r="B248" s="74"/>
       <c r="C248" s="74"/>
       <c r="E248" s="74"/>
       <c r="F248" s="74"/>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="74"/>
       <c r="B249" s="74"/>
       <c r="C249" s="74"/>
       <c r="E249" s="74"/>
       <c r="F249" s="74"/>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="74"/>
       <c r="B250" s="74"/>
       <c r="C250" s="74"/>
       <c r="E250" s="74"/>
       <c r="F250" s="74"/>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="74"/>
       <c r="B251" s="74"/>
       <c r="C251" s="74"/>
       <c r="E251" s="74"/>
       <c r="F251" s="74"/>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" s="74"/>
       <c r="B252" s="74"/>
       <c r="C252" s="74"/>
       <c r="E252" s="74"/>
       <c r="F252" s="74"/>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="74"/>
       <c r="B253" s="74"/>
       <c r="C253" s="74"/>
       <c r="E253" s="74"/>
       <c r="F253" s="74"/>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="74"/>
       <c r="B254" s="74"/>
       <c r="C254" s="74"/>
       <c r="E254" s="74"/>
       <c r="F254" s="74"/>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="74"/>
       <c r="B255" s="74"/>
       <c r="C255" s="74"/>
       <c r="E255" s="74"/>
       <c r="F255" s="74"/>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="74"/>
       <c r="B256" s="74"/>
       <c r="C256" s="74"/>
       <c r="E256" s="74"/>
       <c r="F256" s="74"/>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="74"/>
       <c r="B257" s="74"/>
       <c r="C257" s="74"/>
       <c r="E257" s="74"/>
       <c r="F257" s="74"/>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="74"/>
       <c r="B258" s="74"/>
       <c r="C258" s="74"/>
       <c r="E258" s="74"/>
       <c r="F258" s="74"/>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="74"/>
       <c r="B259" s="74"/>
       <c r="C259" s="74"/>
       <c r="E259" s="74"/>
       <c r="F259" s="74"/>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="74"/>
       <c r="B260" s="74"/>
       <c r="C260" s="74"/>
       <c r="E260" s="74"/>
       <c r="F260" s="74"/>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="74"/>
       <c r="B261" s="74"/>
       <c r="C261" s="74"/>
       <c r="E261" s="74"/>
       <c r="F261" s="74"/>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="74"/>
       <c r="B262" s="74"/>
       <c r="C262" s="74"/>
       <c r="E262" s="74"/>
       <c r="F262" s="74"/>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="74"/>
       <c r="B263" s="74"/>
       <c r="C263" s="74"/>
       <c r="E263" s="74"/>
       <c r="F263" s="74"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="74"/>
       <c r="B264" s="74"/>
       <c r="C264" s="74"/>
       <c r="E264" s="74"/>
       <c r="F264" s="74"/>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="74"/>
       <c r="B265" s="74"/>
       <c r="C265" s="74"/>
       <c r="E265" s="74"/>
       <c r="F265" s="74"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="74"/>
       <c r="B266" s="74"/>
       <c r="C266" s="74"/>
       <c r="E266" s="74"/>
       <c r="F266" s="74"/>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="74"/>
       <c r="B267" s="74"/>
       <c r="C267" s="74"/>
       <c r="E267" s="74"/>
       <c r="F267" s="74"/>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="74"/>
       <c r="B268" s="74"/>
       <c r="C268" s="74"/>
       <c r="E268" s="74"/>
       <c r="F268" s="74"/>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="74"/>
       <c r="B269" s="74"/>
       <c r="C269" s="74"/>
       <c r="E269" s="74"/>
       <c r="F269" s="74"/>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" s="74"/>
       <c r="B270" s="74"/>
       <c r="C270" s="74"/>
       <c r="E270" s="74"/>
       <c r="F270" s="74"/>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="74"/>
       <c r="B271" s="74"/>
       <c r="C271" s="74"/>
       <c r="E271" s="74"/>
       <c r="F271" s="74"/>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="74"/>
       <c r="B272" s="74"/>
       <c r="C272" s="74"/>
       <c r="E272" s="74"/>
       <c r="F272" s="74"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" s="74"/>
       <c r="B273" s="74"/>
       <c r="C273" s="74"/>
       <c r="E273" s="74"/>
       <c r="F273" s="74"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" s="74"/>
       <c r="B274" s="74"/>
       <c r="C274" s="74"/>
       <c r="E274" s="74"/>
       <c r="F274" s="74"/>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" s="74"/>
       <c r="B275" s="74"/>
       <c r="C275" s="74"/>
       <c r="E275" s="74"/>
       <c r="F275" s="74"/>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" s="74"/>
       <c r="B276" s="74"/>
       <c r="C276" s="74"/>
       <c r="E276" s="74"/>
       <c r="F276" s="74"/>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" s="74"/>
       <c r="B277" s="74"/>
       <c r="C277" s="74"/>
       <c r="E277" s="74"/>
       <c r="F277" s="74"/>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" s="74"/>
       <c r="B278" s="74"/>
       <c r="C278" s="74"/>
       <c r="E278" s="74"/>
       <c r="F278" s="74"/>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" s="74"/>
       <c r="B279" s="74"/>
       <c r="C279" s="74"/>
       <c r="E279" s="74"/>
       <c r="F279" s="74"/>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" s="74"/>
       <c r="B280" s="74"/>
       <c r="C280" s="74"/>
       <c r="E280" s="74"/>
       <c r="F280" s="74"/>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" s="74"/>
       <c r="B281" s="74"/>
       <c r="C281" s="74"/>
       <c r="E281" s="74"/>
       <c r="F281" s="74"/>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" s="74"/>
       <c r="B282" s="74"/>
       <c r="C282" s="74"/>
       <c r="E282" s="74"/>
       <c r="F282" s="74"/>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" s="74"/>
       <c r="B283" s="74"/>
       <c r="C283" s="74"/>
       <c r="E283" s="74"/>
       <c r="F283" s="74"/>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" s="74"/>
       <c r="B284" s="74"/>
       <c r="C284" s="74"/>
       <c r="E284" s="74"/>
       <c r="F284" s="74"/>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" s="74"/>
       <c r="B285" s="74"/>
       <c r="C285" s="74"/>
       <c r="E285" s="74"/>
       <c r="F285" s="74"/>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" s="74"/>
       <c r="B286" s="74"/>
       <c r="C286" s="74"/>
       <c r="E286" s="74"/>
       <c r="F286" s="74"/>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" s="74"/>
       <c r="B287" s="74"/>
       <c r="C287" s="74"/>
       <c r="E287" s="74"/>
       <c r="F287" s="74"/>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" s="74"/>
       <c r="B288" s="74"/>
       <c r="C288" s="74"/>
       <c r="E288" s="74"/>
       <c r="F288" s="74"/>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="74"/>
       <c r="B289" s="74"/>
       <c r="C289" s="74"/>
       <c r="E289" s="74"/>
       <c r="F289" s="74"/>
     </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" s="74"/>
       <c r="B290" s="74"/>
       <c r="C290" s="74"/>
       <c r="E290" s="74"/>
       <c r="F290" s="74"/>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" s="74"/>
       <c r="B291" s="74"/>
       <c r="C291" s="74"/>
       <c r="E291" s="74"/>
       <c r="F291" s="74"/>
     </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" s="74"/>
       <c r="B292" s="74"/>
       <c r="C292" s="74"/>
       <c r="E292" s="74"/>
       <c r="F292" s="74"/>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" s="74"/>
       <c r="B293" s="74"/>
       <c r="C293" s="74"/>
       <c r="E293" s="74"/>
       <c r="F293" s="74"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" s="74"/>
       <c r="B294" s="74"/>
       <c r="C294" s="74"/>
       <c r="E294" s="74"/>
       <c r="F294" s="74"/>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" s="74"/>
       <c r="B295" s="74"/>
       <c r="C295" s="74"/>
       <c r="E295" s="74"/>
       <c r="F295" s="74"/>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" s="74"/>
       <c r="B296" s="74"/>
       <c r="C296" s="74"/>
       <c r="E296" s="74"/>
       <c r="F296" s="74"/>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" s="74"/>
       <c r="B297" s="74"/>
       <c r="C297" s="74"/>
       <c r="E297" s="74"/>
       <c r="F297" s="74"/>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" s="74"/>
       <c r="B298" s="74"/>
       <c r="C298" s="74"/>
       <c r="E298" s="74"/>
       <c r="F298" s="74"/>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" s="74"/>
       <c r="B299" s="74"/>
       <c r="C299" s="74"/>
       <c r="E299" s="74"/>
       <c r="F299" s="74"/>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" s="74"/>
       <c r="B300" s="74"/>
       <c r="C300" s="74"/>
       <c r="E300" s="74"/>
       <c r="F300" s="74"/>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" s="74"/>
       <c r="B301" s="74"/>
       <c r="C301" s="74"/>
       <c r="E301" s="74"/>
       <c r="F301" s="74"/>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" s="74"/>
       <c r="B302" s="74"/>
       <c r="C302" s="74"/>
       <c r="E302" s="74"/>
       <c r="F302" s="74"/>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" s="74"/>
       <c r="B303" s="74"/>
       <c r="C303" s="74"/>
       <c r="E303" s="74"/>
       <c r="F303" s="74"/>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" s="74"/>
       <c r="B304" s="74"/>
       <c r="C304" s="74"/>
       <c r="E304" s="74"/>
       <c r="F304" s="74"/>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" s="74"/>
       <c r="B305" s="74"/>
       <c r="C305" s="74"/>
       <c r="E305" s="74"/>
       <c r="F305" s="74"/>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" s="74"/>
       <c r="B306" s="74"/>
       <c r="C306" s="74"/>
       <c r="E306" s="74"/>
       <c r="F306" s="74"/>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" s="74"/>
       <c r="B307" s="74"/>
       <c r="C307" s="74"/>
       <c r="E307" s="74"/>
       <c r="F307" s="74"/>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" s="74"/>
       <c r="B308" s="74"/>
       <c r="C308" s="74"/>
       <c r="E308" s="74"/>
       <c r="F308" s="74"/>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" s="74"/>
       <c r="B309" s="74"/>
       <c r="C309" s="74"/>
       <c r="E309" s="74"/>
       <c r="F309" s="74"/>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" s="74"/>
       <c r="B310" s="74"/>
       <c r="C310" s="74"/>
       <c r="E310" s="74"/>
       <c r="F310" s="74"/>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" s="74"/>
       <c r="B311" s="74"/>
       <c r="C311" s="74"/>
       <c r="E311" s="74"/>
       <c r="F311" s="74"/>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" s="74"/>
       <c r="B312" s="74"/>
       <c r="C312" s="74"/>
       <c r="E312" s="74"/>
       <c r="F312" s="74"/>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" s="74"/>
       <c r="B313" s="74"/>
       <c r="C313" s="74"/>
       <c r="E313" s="74"/>
       <c r="F313" s="74"/>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" s="74"/>
       <c r="B314" s="74"/>
       <c r="C314" s="74"/>
       <c r="E314" s="74"/>
       <c r="F314" s="74"/>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" s="74"/>
       <c r="B315" s="74"/>
       <c r="C315" s="74"/>
       <c r="E315" s="74"/>
       <c r="F315" s="74"/>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" s="74"/>
       <c r="B316" s="74"/>
       <c r="C316" s="74"/>
       <c r="E316" s="74"/>
       <c r="F316" s="74"/>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" s="74"/>
       <c r="B317" s="74"/>
       <c r="C317" s="74"/>
       <c r="E317" s="74"/>
       <c r="F317" s="74"/>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" s="74"/>
       <c r="B318" s="74"/>
       <c r="C318" s="74"/>
       <c r="E318" s="74"/>
       <c r="F318" s="74"/>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" s="74"/>
       <c r="B319" s="74"/>
       <c r="C319" s="74"/>
       <c r="E319" s="74"/>
       <c r="F319" s="74"/>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" s="74"/>
       <c r="B320" s="74"/>
       <c r="C320" s="74"/>
       <c r="E320" s="74"/>
       <c r="F320" s="74"/>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" s="74"/>
       <c r="B321" s="74"/>
       <c r="C321" s="74"/>
       <c r="E321" s="74"/>
       <c r="F321" s="74"/>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" s="74"/>
       <c r="B322" s="74"/>
       <c r="C322" s="74"/>
       <c r="E322" s="74"/>
       <c r="F322" s="74"/>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" s="74"/>
       <c r="B323" s="74"/>
       <c r="C323" s="74"/>
       <c r="E323" s="74"/>
       <c r="F323" s="74"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" s="74"/>
       <c r="B324" s="74"/>
       <c r="C324" s="74"/>
       <c r="E324" s="74"/>
       <c r="F324" s="74"/>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" s="74"/>
       <c r="B325" s="74"/>
       <c r="C325" s="74"/>
       <c r="E325" s="74"/>
       <c r="F325" s="74"/>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" s="74"/>
       <c r="B326" s="74"/>
       <c r="C326" s="74"/>
       <c r="E326" s="74"/>
       <c r="F326" s="74"/>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" s="74"/>
       <c r="B327" s="74"/>
       <c r="C327" s="74"/>
       <c r="E327" s="74"/>
       <c r="F327" s="74"/>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" s="74"/>
       <c r="B328" s="74"/>
       <c r="C328" s="74"/>
       <c r="E328" s="74"/>
       <c r="F328" s="74"/>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" s="74"/>
       <c r="B329" s="74"/>
       <c r="C329" s="74"/>
       <c r="E329" s="74"/>
       <c r="F329" s="74"/>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" s="74"/>
       <c r="B330" s="74"/>
       <c r="C330" s="74"/>
       <c r="E330" s="74"/>
       <c r="F330" s="74"/>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" s="74"/>
       <c r="B331" s="74"/>
       <c r="C331" s="74"/>
       <c r="E331" s="74"/>
       <c r="F331" s="74"/>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" s="74"/>
       <c r="B332" s="74"/>
       <c r="C332" s="74"/>
       <c r="E332" s="74"/>
       <c r="F332" s="74"/>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" s="74"/>
       <c r="B333" s="74"/>
       <c r="C333" s="74"/>
       <c r="E333" s="74"/>
       <c r="F333" s="74"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" s="74"/>
       <c r="B334" s="74"/>
       <c r="C334" s="74"/>
       <c r="E334" s="74"/>
       <c r="F334" s="74"/>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" s="74"/>
       <c r="B335" s="74"/>
       <c r="C335" s="74"/>
       <c r="E335" s="74"/>
       <c r="F335" s="74"/>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" s="74"/>
       <c r="B336" s="74"/>
       <c r="C336" s="74"/>
       <c r="E336" s="74"/>
       <c r="F336" s="74"/>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" s="74"/>
       <c r="B337" s="74"/>
       <c r="C337" s="74"/>
       <c r="E337" s="74"/>
       <c r="F337" s="74"/>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" s="74"/>
       <c r="B338" s="74"/>
       <c r="C338" s="74"/>
       <c r="E338" s="74"/>
       <c r="F338" s="74"/>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" s="74"/>
       <c r="B339" s="74"/>
       <c r="C339" s="74"/>
       <c r="E339" s="74"/>
       <c r="F339" s="74"/>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" s="74"/>
       <c r="B340" s="74"/>
       <c r="C340" s="74"/>
       <c r="E340" s="74"/>
       <c r="F340" s="74"/>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" s="74"/>
       <c r="B341" s="74"/>
       <c r="C341" s="74"/>
       <c r="E341" s="74"/>
       <c r="F341" s="74"/>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" s="74"/>
       <c r="B342" s="74"/>
       <c r="C342" s="74"/>
       <c r="E342" s="74"/>
       <c r="F342" s="74"/>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" s="74"/>
       <c r="B343" s="74"/>
       <c r="C343" s="74"/>
       <c r="E343" s="74"/>
       <c r="F343" s="74"/>
     </row>
-    <row r="344" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" s="74"/>
       <c r="B344" s="74"/>
       <c r="C344" s="74"/>
       <c r="E344" s="74"/>
       <c r="F344" s="74"/>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" s="74"/>
       <c r="B345" s="74"/>
       <c r="C345" s="74"/>
       <c r="E345" s="74"/>
       <c r="F345" s="74"/>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" s="74"/>
       <c r="B346" s="74"/>
       <c r="C346" s="74"/>
       <c r="E346" s="74"/>
       <c r="F346" s="74"/>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" s="74"/>
       <c r="B347" s="74"/>
       <c r="C347" s="74"/>
       <c r="E347" s="74"/>
       <c r="F347" s="74"/>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" s="74"/>
       <c r="B348" s="74"/>
       <c r="C348" s="74"/>
       <c r="E348" s="74"/>
       <c r="F348" s="74"/>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" s="74"/>
       <c r="B349" s="74"/>
       <c r="C349" s="74"/>
       <c r="E349" s="74"/>
       <c r="F349" s="74"/>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" s="74"/>
       <c r="B350" s="74"/>
       <c r="C350" s="74"/>
       <c r="E350" s="74"/>
       <c r="F350" s="74"/>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" s="74"/>
       <c r="B351" s="74"/>
       <c r="C351" s="74"/>
       <c r="E351" s="74"/>
       <c r="F351" s="74"/>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" s="74"/>
       <c r="B352" s="74"/>
       <c r="C352" s="74"/>
       <c r="E352" s="74"/>
       <c r="F352" s="74"/>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" s="74"/>
       <c r="B353" s="74"/>
       <c r="C353" s="74"/>
       <c r="E353" s="74"/>
       <c r="F353" s="74"/>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" s="74"/>
       <c r="B354" s="74"/>
       <c r="C354" s="74"/>
       <c r="E354" s="74"/>
       <c r="F354" s="74"/>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" s="74"/>
       <c r="B355" s="74"/>
       <c r="C355" s="74"/>
       <c r="E355" s="74"/>
       <c r="F355" s="74"/>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" s="74"/>
       <c r="B356" s="74"/>
       <c r="C356" s="74"/>
       <c r="E356" s="74"/>
       <c r="F356" s="74"/>
     </row>
-    <row r="357" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" s="74"/>
       <c r="B357" s="74"/>
       <c r="C357" s="74"/>
       <c r="E357" s="74"/>
       <c r="F357" s="74"/>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" s="74"/>
       <c r="B358" s="74"/>
       <c r="C358" s="74"/>
       <c r="E358" s="74"/>
       <c r="F358" s="74"/>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" s="74"/>
       <c r="B359" s="74"/>
       <c r="C359" s="74"/>
       <c r="E359" s="74"/>
       <c r="F359" s="74"/>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" s="74"/>
       <c r="B360" s="74"/>
       <c r="C360" s="74"/>
       <c r="E360" s="74"/>
       <c r="F360" s="74"/>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" s="74"/>
       <c r="B361" s="74"/>
       <c r="C361" s="74"/>
       <c r="E361" s="74"/>
       <c r="F361" s="74"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" s="74"/>
       <c r="B362" s="74"/>
       <c r="C362" s="74"/>
       <c r="E362" s="74"/>
       <c r="F362" s="74"/>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" s="74"/>
       <c r="B363" s="74"/>
       <c r="C363" s="74"/>
       <c r="E363" s="74"/>
       <c r="F363" s="74"/>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" s="74"/>
       <c r="B364" s="74"/>
       <c r="C364" s="74"/>
       <c r="E364" s="74"/>
       <c r="F364" s="74"/>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" s="74"/>
       <c r="B365" s="74"/>
       <c r="C365" s="74"/>
       <c r="E365" s="74"/>
       <c r="F365" s="74"/>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" s="74"/>
       <c r="B366" s="74"/>
       <c r="C366" s="74"/>
       <c r="E366" s="74"/>
       <c r="F366" s="74"/>
     </row>
-    <row r="367" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" s="74"/>
       <c r="B367" s="74"/>
       <c r="C367" s="74"/>
       <c r="E367" s="74"/>
       <c r="F367" s="74"/>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" s="74"/>
       <c r="B368" s="74"/>
       <c r="C368" s="74"/>
       <c r="E368" s="74"/>
       <c r="F368" s="74"/>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" s="74"/>
       <c r="B369" s="74"/>
       <c r="C369" s="74"/>
       <c r="E369" s="74"/>
       <c r="F369" s="74"/>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" s="74"/>
       <c r="B370" s="74"/>
       <c r="C370" s="74"/>
       <c r="E370" s="74"/>
       <c r="F370" s="74"/>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" s="74"/>
       <c r="B371" s="74"/>
       <c r="C371" s="74"/>
       <c r="E371" s="74"/>
       <c r="F371" s="74"/>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" s="74"/>
       <c r="B372" s="74"/>
       <c r="C372" s="74"/>
       <c r="E372" s="74"/>
       <c r="F372" s="74"/>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" s="74"/>
       <c r="B373" s="74"/>
       <c r="C373" s="74"/>
       <c r="E373" s="74"/>
       <c r="F373" s="74"/>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" s="74"/>
       <c r="B374" s="74"/>
       <c r="C374" s="74"/>
       <c r="E374" s="74"/>
       <c r="F374" s="74"/>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" s="74"/>
       <c r="B375" s="74"/>
       <c r="C375" s="74"/>
       <c r="E375" s="74"/>
       <c r="F375" s="74"/>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" s="74"/>
       <c r="B376" s="74"/>
       <c r="C376" s="74"/>
       <c r="E376" s="74"/>
       <c r="F376" s="74"/>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" s="74"/>
       <c r="B377" s="74"/>
       <c r="C377" s="74"/>
       <c r="E377" s="74"/>
       <c r="F377" s="74"/>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" s="74"/>
       <c r="B378" s="74"/>
       <c r="C378" s="74"/>
       <c r="E378" s="74"/>
       <c r="F378" s="74"/>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" s="74"/>
       <c r="B379" s="74"/>
       <c r="C379" s="74"/>
       <c r="E379" s="74"/>
       <c r="F379" s="74"/>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" s="74"/>
       <c r="B380" s="74"/>
       <c r="C380" s="74"/>
       <c r="E380" s="74"/>
       <c r="F380" s="74"/>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" s="74"/>
       <c r="B381" s="74"/>
       <c r="C381" s="74"/>
       <c r="E381" s="74"/>
       <c r="F381" s="74"/>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" s="74"/>
       <c r="B382" s="74"/>
       <c r="C382" s="74"/>
       <c r="E382" s="74"/>
       <c r="F382" s="74"/>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" s="74"/>
       <c r="B383" s="74"/>
       <c r="C383" s="74"/>
       <c r="E383" s="74"/>
       <c r="F383" s="74"/>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" s="74"/>
       <c r="B384" s="74"/>
       <c r="C384" s="74"/>
       <c r="E384" s="74"/>
       <c r="F384" s="74"/>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" s="74"/>
       <c r="B385" s="74"/>
       <c r="C385" s="74"/>
       <c r="E385" s="74"/>
       <c r="F385" s="74"/>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" s="74"/>
       <c r="B386" s="74"/>
       <c r="C386" s="74"/>
       <c r="E386" s="74"/>
       <c r="F386" s="74"/>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" s="74"/>
       <c r="B387" s="74"/>
       <c r="C387" s="74"/>
       <c r="E387" s="74"/>
       <c r="F387" s="74"/>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" s="74"/>
       <c r="B388" s="74"/>
       <c r="C388" s="74"/>
       <c r="E388" s="74"/>
       <c r="F388" s="74"/>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" s="74"/>
       <c r="B389" s="74"/>
       <c r="C389" s="74"/>
       <c r="E389" s="74"/>
       <c r="F389" s="74"/>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" s="74"/>
       <c r="B390" s="74"/>
       <c r="C390" s="74"/>
       <c r="E390" s="74"/>
       <c r="F390" s="74"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" s="74"/>
       <c r="B391" s="74"/>
       <c r="C391" s="74"/>
       <c r="E391" s="74"/>
       <c r="F391" s="74"/>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" s="74"/>
       <c r="B392" s="74"/>
       <c r="C392" s="74"/>
       <c r="E392" s="74"/>
       <c r="F392" s="74"/>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" s="74"/>
       <c r="B393" s="74"/>
       <c r="C393" s="74"/>
       <c r="E393" s="74"/>
       <c r="F393" s="74"/>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" s="74"/>
       <c r="B394" s="74"/>
       <c r="C394" s="74"/>
       <c r="E394" s="74"/>
       <c r="F394" s="74"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" s="74"/>
       <c r="B395" s="74"/>
       <c r="C395" s="74"/>
       <c r="E395" s="74"/>
       <c r="F395" s="74"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" s="74"/>
       <c r="B396" s="74"/>
       <c r="C396" s="74"/>
       <c r="E396" s="74"/>
       <c r="F396" s="74"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" s="74"/>
       <c r="B397" s="74"/>
       <c r="C397" s="74"/>
       <c r="E397" s="74"/>
       <c r="F397" s="74"/>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" s="74"/>
       <c r="B398" s="74"/>
       <c r="C398" s="74"/>
       <c r="E398" s="74"/>
       <c r="F398" s="74"/>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" s="74"/>
       <c r="B399" s="74"/>
       <c r="C399" s="74"/>
       <c r="E399" s="74"/>
       <c r="F399" s="74"/>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" s="74"/>
       <c r="B400" s="74"/>
       <c r="C400" s="74"/>
       <c r="E400" s="74"/>
       <c r="F400" s="74"/>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" s="74"/>
       <c r="B401" s="74"/>
       <c r="C401" s="74"/>
       <c r="E401" s="74"/>
       <c r="F401" s="74"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A402" s="74"/>
       <c r="B402" s="74"/>
       <c r="C402" s="74"/>
       <c r="E402" s="74"/>
       <c r="F402" s="74"/>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" s="74"/>
       <c r="B403" s="74"/>
       <c r="C403" s="74"/>
       <c r="E403" s="74"/>
       <c r="F403" s="74"/>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" s="74"/>
       <c r="B404" s="74"/>
       <c r="C404" s="74"/>
       <c r="E404" s="74"/>
       <c r="F404" s="74"/>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" s="74"/>
       <c r="B405" s="74"/>
       <c r="C405" s="74"/>
       <c r="E405" s="74"/>
       <c r="F405" s="74"/>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" s="74"/>
       <c r="B406" s="74"/>
       <c r="C406" s="74"/>
       <c r="E406" s="74"/>
       <c r="F406" s="74"/>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" s="74"/>
       <c r="B407" s="74"/>
       <c r="C407" s="74"/>
       <c r="E407" s="74"/>
       <c r="F407" s="74"/>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" s="74"/>
       <c r="B408" s="74"/>
       <c r="C408" s="74"/>
       <c r="E408" s="74"/>
       <c r="F408" s="74"/>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" s="74"/>
       <c r="B409" s="74"/>
       <c r="C409" s="74"/>
       <c r="E409" s="74"/>
       <c r="F409" s="74"/>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" s="74"/>
       <c r="B410" s="74"/>
       <c r="C410" s="74"/>
       <c r="E410" s="74"/>
       <c r="F410" s="74"/>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A411" s="74"/>
       <c r="B411" s="74"/>
       <c r="C411" s="74"/>
       <c r="E411" s="74"/>
       <c r="F411" s="74"/>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A412" s="74"/>
       <c r="B412" s="74"/>
       <c r="C412" s="74"/>
       <c r="E412" s="74"/>
       <c r="F412" s="74"/>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A413" s="74"/>
       <c r="B413" s="74"/>
       <c r="C413" s="74"/>
